--- a/data/VNQ.xlsx
+++ b/data/VNQ.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.52353668212891</v>
+        <v>55.52354049682617</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.91171646118164</v>
+        <v>55.91170501708984</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.5662727355957</v>
+        <v>56.56628036499023</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.12189102172852</v>
+        <v>57.12189483642578</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58.30162048339844</v>
+        <v>58.30164337158203</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58.21789169311523</v>
+        <v>58.21791458129883</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.00944900512695</v>
+        <v>59.00946426391602</v>
       </c>
     </row>
     <row r="9">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.97902297973633</v>
+        <v>58.97901153564453</v>
       </c>
     </row>
     <row r="11">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.96086883544922</v>
+        <v>59.96085357666016</v>
       </c>
     </row>
     <row r="13">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.25009536743164</v>
+        <v>60.25008773803711</v>
       </c>
     </row>
     <row r="14">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.45558547973633</v>
+        <v>60.45560073852539</v>
       </c>
     </row>
     <row r="15">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60.27292251586914</v>
+        <v>60.27291488647461</v>
       </c>
     </row>
     <row r="16">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60.280517578125</v>
+        <v>60.28051376342773</v>
       </c>
     </row>
     <row r="17">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.48603439331055</v>
+        <v>60.48602294921875</v>
       </c>
     </row>
     <row r="18">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.23952865600586</v>
+        <v>61.23954010009766</v>
       </c>
     </row>
     <row r="19">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61.84081268310547</v>
+        <v>61.84081649780273</v>
       </c>
     </row>
     <row r="20">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62.32793045043945</v>
+        <v>62.32792663574219</v>
       </c>
     </row>
     <row r="21">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62.83028411865234</v>
+        <v>62.83027648925781</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63.48483657836914</v>
+        <v>63.48482894897461</v>
       </c>
     </row>
     <row r="23">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63.0814323425293</v>
+        <v>63.08144378662109</v>
       </c>
     </row>
     <row r="24">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.55331420898438</v>
+        <v>63.55334091186523</v>
       </c>
     </row>
     <row r="25">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63.91866683959961</v>
+        <v>63.91868591308594</v>
       </c>
     </row>
     <row r="26">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63.50004196166992</v>
+        <v>63.50006866455078</v>
       </c>
     </row>
     <row r="27">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.02521514892578</v>
+        <v>64.02522277832031</v>
       </c>
     </row>
     <row r="28">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64.02521514892578</v>
+        <v>64.02522277832031</v>
       </c>
     </row>
     <row r="29">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.79690551757812</v>
+        <v>63.79689025878906</v>
       </c>
     </row>
     <row r="31">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64.1241455078125</v>
+        <v>64.12417602539062</v>
       </c>
     </row>
     <row r="32">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64.32965087890625</v>
+        <v>64.32968902587891</v>
       </c>
     </row>
     <row r="33">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64.76350402832031</v>
+        <v>64.76353454589844</v>
       </c>
     </row>
     <row r="34">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>64.74830627441406</v>
+        <v>64.74829864501953</v>
       </c>
     </row>
     <row r="35">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>64.40576934814453</v>
+        <v>64.40577697753906</v>
       </c>
     </row>
     <row r="37">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>64.78634643554688</v>
+        <v>64.78636169433594</v>
       </c>
     </row>
     <row r="38">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>64.27642059326172</v>
+        <v>64.27639770507812</v>
       </c>
     </row>
     <row r="39">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64.0784912109375</v>
+        <v>64.07850646972656</v>
       </c>
     </row>
     <row r="40">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>63.75884246826172</v>
+        <v>63.75883102416992</v>
       </c>
     </row>
     <row r="41">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>63.72836685180664</v>
+        <v>63.72841644287109</v>
       </c>
     </row>
     <row r="43">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>64.01763153076172</v>
+        <v>64.01761627197266</v>
       </c>
     </row>
     <row r="44">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>64.19267272949219</v>
+        <v>64.19265747070312</v>
       </c>
     </row>
     <row r="45">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>63.89583587646484</v>
+        <v>63.89582443237305</v>
       </c>
     </row>
     <row r="46">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63.75884246826172</v>
+        <v>63.75883102416992</v>
       </c>
     </row>
     <row r="47">
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63.82732009887695</v>
+        <v>63.82732772827148</v>
       </c>
     </row>
     <row r="48">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>64.76350402832031</v>
+        <v>64.76353454589844</v>
       </c>
     </row>
     <row r="49">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65.06034088134766</v>
+        <v>65.06035614013672</v>
       </c>
     </row>
     <row r="50">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65.38002777099609</v>
+        <v>65.38003540039062</v>
       </c>
     </row>
     <row r="51">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65.47897338867188</v>
+        <v>65.47896575927734</v>
       </c>
     </row>
     <row r="52">
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>64.94617462158203</v>
+        <v>64.94618225097656</v>
       </c>
     </row>
     <row r="54">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>64.74830627441406</v>
+        <v>64.74829864501953</v>
       </c>
     </row>
     <row r="55">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>64.94617462158203</v>
+        <v>64.94618225097656</v>
       </c>
     </row>
     <row r="56">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.10308074951172</v>
+        <v>66.10308837890625</v>
       </c>
     </row>
     <row r="57">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>65.70729827880859</v>
+        <v>65.70729064941406</v>
       </c>
     </row>
     <row r="59">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>66.23246002197266</v>
+        <v>66.23246765136719</v>
       </c>
     </row>
     <row r="60">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>66.04219818115234</v>
+        <v>66.04216003417969</v>
       </c>
     </row>
     <row r="61">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>66.68304443359375</v>
+        <v>66.68302154541016</v>
       </c>
     </row>
     <row r="62">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>66.62171173095703</v>
+        <v>66.62172698974609</v>
       </c>
     </row>
     <row r="63">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>66.58340454101562</v>
+        <v>66.58338165283203</v>
       </c>
     </row>
     <row r="64">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>67.05098724365234</v>
+        <v>67.05097961425781</v>
       </c>
     </row>
     <row r="65">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>66.97432708740234</v>
+        <v>66.97430419921875</v>
       </c>
     </row>
     <row r="66">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>67.33460998535156</v>
+        <v>67.33460235595703</v>
       </c>
     </row>
     <row r="68">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>66.95900726318359</v>
+        <v>66.95899963378906</v>
       </c>
     </row>
     <row r="69">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>66.60637664794922</v>
+        <v>66.60636901855469</v>
       </c>
     </row>
     <row r="70">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>67.21962738037109</v>
+        <v>67.21965026855469</v>
       </c>
     </row>
     <row r="71">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>67.17362976074219</v>
+        <v>67.17362213134766</v>
       </c>
     </row>
     <row r="72">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>67.15065765380859</v>
+        <v>67.15061950683594</v>
       </c>
     </row>
     <row r="74">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>65.63285827636719</v>
+        <v>65.63283538818359</v>
       </c>
     </row>
     <row r="75">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>65.53319549560547</v>
+        <v>65.53318786621094</v>
       </c>
     </row>
     <row r="77">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>66.15411376953125</v>
+        <v>66.15412139892578</v>
       </c>
     </row>
     <row r="80">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>66.53739166259766</v>
+        <v>66.53737640380859</v>
       </c>
     </row>
     <row r="82">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>65.88579559326172</v>
+        <v>65.88581085205078</v>
       </c>
     </row>
     <row r="83">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>66.51441192626953</v>
+        <v>66.51435852050781</v>
       </c>
     </row>
     <row r="84">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>65.77845764160156</v>
+        <v>65.77848052978516</v>
       </c>
     </row>
     <row r="89">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>65.70949554443359</v>
+        <v>65.70951080322266</v>
       </c>
     </row>
     <row r="90">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>65.87814331054688</v>
+        <v>65.87815093994141</v>
       </c>
     </row>
     <row r="91">
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>66.58340454101562</v>
+        <v>66.58338165283203</v>
       </c>
     </row>
     <row r="92">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>66.51441192626953</v>
+        <v>66.51435852050781</v>
       </c>
     </row>
     <row r="93">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>67.21195220947266</v>
+        <v>67.21197509765625</v>
       </c>
     </row>
     <row r="95">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>67.48023223876953</v>
+        <v>67.48025512695312</v>
       </c>
     </row>
     <row r="96">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>67.34995269775391</v>
+        <v>67.34993743896484</v>
       </c>
     </row>
     <row r="97">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>66.37638854980469</v>
+        <v>66.37640380859375</v>
       </c>
     </row>
     <row r="98">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>66.94366455078125</v>
+        <v>66.94367218017578</v>
       </c>
     </row>
     <row r="99">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>67.1429443359375</v>
+        <v>67.14296722412109</v>
       </c>
     </row>
     <row r="100">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>67.29628753662109</v>
+        <v>67.29627990722656</v>
       </c>
     </row>
     <row r="101">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>67.50328063964844</v>
+        <v>67.50326538085938</v>
       </c>
     </row>
     <row r="102">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>66.83633422851562</v>
+        <v>66.83632659912109</v>
       </c>
     </row>
     <row r="103">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>65.9471435546875</v>
+        <v>65.94713592529297</v>
       </c>
     </row>
     <row r="104">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>66.22309875488281</v>
+        <v>66.22309112548828</v>
       </c>
     </row>
     <row r="105">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>66.60637664794922</v>
+        <v>66.60636901855469</v>
       </c>
     </row>
     <row r="106">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>66.76735687255859</v>
+        <v>66.76734924316406</v>
       </c>
     </row>
     <row r="107">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>66.46840667724609</v>
+        <v>66.46839141845703</v>
       </c>
     </row>
     <row r="108">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>67.85587310791016</v>
+        <v>67.85586547851562</v>
       </c>
     </row>
     <row r="109">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>67.9862060546875</v>
+        <v>67.98618316650391</v>
       </c>
     </row>
     <row r="110">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>68.23915863037109</v>
+        <v>68.23914337158203</v>
       </c>
     </row>
     <row r="111">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>68.2008056640625</v>
+        <v>68.20081329345703</v>
       </c>
     </row>
     <row r="113">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>68.72206878662109</v>
+        <v>68.72208404541016</v>
       </c>
     </row>
     <row r="115">
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>69.49629974365234</v>
+        <v>69.49630737304688</v>
       </c>
     </row>
     <row r="117">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>69.42731475830078</v>
+        <v>69.42732238769531</v>
       </c>
     </row>
     <row r="118">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>69.80293273925781</v>
+        <v>69.80291748046875</v>
       </c>
     </row>
     <row r="119">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>69.16670989990234</v>
+        <v>69.16667938232422</v>
       </c>
     </row>
     <row r="121">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>67.90951538085938</v>
+        <v>67.90952301025391</v>
       </c>
     </row>
     <row r="123">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>66.55271148681641</v>
+        <v>66.55270385742188</v>
       </c>
     </row>
     <row r="124">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>67.64165496826172</v>
+        <v>67.64164733886719</v>
       </c>
     </row>
     <row r="126">
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>68.78706359863281</v>
+        <v>68.78707122802734</v>
       </c>
     </row>
     <row r="128">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>69.60744476318359</v>
+        <v>69.607421875</v>
       </c>
     </row>
     <row r="129">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>69.35977935791016</v>
+        <v>69.35976409912109</v>
       </c>
     </row>
     <row r="130">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>69.60744476318359</v>
+        <v>69.607421875</v>
       </c>
     </row>
     <row r="131">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>69.839599609375</v>
+        <v>69.83958435058594</v>
       </c>
     </row>
     <row r="132">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>70.2420654296875</v>
+        <v>70.24204254150391</v>
       </c>
     </row>
     <row r="133">
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>69.32883453369141</v>
+        <v>69.32881927490234</v>
       </c>
     </row>
     <row r="134">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>69.1817626953125</v>
+        <v>69.18177032470703</v>
       </c>
     </row>
     <row r="136">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>69.01924133300781</v>
+        <v>69.01923370361328</v>
       </c>
     </row>
     <row r="137">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>68.78706359863281</v>
+        <v>68.78707122802734</v>
       </c>
     </row>
     <row r="138">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>68.78706359863281</v>
+        <v>68.78707122802734</v>
       </c>
     </row>
     <row r="139">
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>67.66486358642578</v>
+        <v>67.66487121582031</v>
       </c>
     </row>
     <row r="140">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>68.36912536621094</v>
+        <v>68.36911773681641</v>
       </c>
     </row>
     <row r="142">
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>68.02086639404297</v>
+        <v>68.02085113525391</v>
       </c>
     </row>
     <row r="144">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>68.3304443359375</v>
+        <v>68.33043670654297</v>
       </c>
     </row>
     <row r="145">
@@ -1865,7 +1865,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>68.51618194580078</v>
+        <v>68.51616668701172</v>
       </c>
     </row>
     <row r="146">
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>68.7947998046875</v>
+        <v>68.79480743408203</v>
       </c>
     </row>
     <row r="148">
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>68.7947998046875</v>
+        <v>68.79480743408203</v>
       </c>
     </row>
     <row r="149">
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>69.12760162353516</v>
+        <v>69.12760925292969</v>
       </c>
     </row>
     <row r="150">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>67.76547241210938</v>
+        <v>67.76546478271484</v>
       </c>
     </row>
     <row r="151">
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>68.51618194580078</v>
+        <v>68.51616668701172</v>
       </c>
     </row>
     <row r="152">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>69.1817626953125</v>
+        <v>69.18177032470703</v>
       </c>
     </row>
     <row r="153">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>70.39687347412109</v>
+        <v>70.39683532714844</v>
       </c>
     </row>
     <row r="154">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>70.22659301757812</v>
+        <v>70.22657775878906</v>
       </c>
     </row>
     <row r="157">
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>69.84735107421875</v>
+        <v>69.84733581542969</v>
       </c>
     </row>
     <row r="159">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>71.07790374755859</v>
+        <v>71.077880859375</v>
       </c>
     </row>
     <row r="161">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>70.57484436035156</v>
+        <v>70.57485198974609</v>
       </c>
     </row>
     <row r="162">
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>70.86894226074219</v>
+        <v>70.86892700195312</v>
       </c>
     </row>
     <row r="163">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>71.19399261474609</v>
+        <v>71.19400024414062</v>
       </c>
     </row>
     <row r="164">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>70.73736572265625</v>
+        <v>70.73737335205078</v>
       </c>
     </row>
     <row r="166">
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>70.53615570068359</v>
+        <v>70.53614044189453</v>
       </c>
     </row>
     <row r="167">
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>70.76831817626953</v>
+        <v>70.768310546875</v>
       </c>
     </row>
     <row r="168">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>71.31783294677734</v>
+        <v>71.31782531738281</v>
       </c>
     </row>
     <row r="169">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>71.37199401855469</v>
+        <v>71.37198638916016</v>
       </c>
     </row>
     <row r="170">
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>72.08400726318359</v>
+        <v>72.08401489257812</v>
       </c>
     </row>
     <row r="171">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>72.68767547607422</v>
+        <v>72.68768310546875</v>
       </c>
     </row>
     <row r="172">
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>72.16140747070312</v>
+        <v>72.16139984130859</v>
       </c>
     </row>
     <row r="173">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>72.32390594482422</v>
+        <v>72.32392883300781</v>
       </c>
     </row>
     <row r="174">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>71.97566223144531</v>
+        <v>71.97565460205078</v>
       </c>
     </row>
     <row r="175">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>71.68929290771484</v>
+        <v>71.68930053710938</v>
       </c>
     </row>
     <row r="178">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>70.92312622070312</v>
+        <v>70.92311859130859</v>
       </c>
     </row>
     <row r="179">
@@ -2205,7 +2205,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>71.54224395751953</v>
+        <v>71.54225158691406</v>
       </c>
     </row>
     <row r="180">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>72.31617736816406</v>
+        <v>72.31618499755859</v>
       </c>
     </row>
     <row r="181">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>72.06853485107422</v>
+        <v>72.06855010986328</v>
       </c>
     </row>
     <row r="182">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>72.32390594482422</v>
+        <v>72.32392883300781</v>
       </c>
     </row>
     <row r="183">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>72.32390594482422</v>
+        <v>72.32392883300781</v>
       </c>
     </row>
     <row r="184">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>72.44001770019531</v>
+        <v>72.44001007080078</v>
       </c>
     </row>
     <row r="185">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>72.27931976318359</v>
+        <v>72.27930450439453</v>
       </c>
     </row>
     <row r="186">
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>72.41971588134766</v>
+        <v>72.41973876953125</v>
       </c>
     </row>
     <row r="187">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>73.02824401855469</v>
+        <v>73.02825164794922</v>
       </c>
     </row>
     <row r="188">
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>72.62255859375</v>
+        <v>72.62256622314453</v>
       </c>
     </row>
     <row r="189">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>72.74739074707031</v>
+        <v>72.74738311767578</v>
       </c>
     </row>
     <row r="190">
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>71.75661468505859</v>
+        <v>71.75662231445312</v>
       </c>
     </row>
     <row r="192">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>72.45094299316406</v>
+        <v>72.45092010498047</v>
       </c>
     </row>
     <row r="193">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>72.88780212402344</v>
+        <v>72.88780975341797</v>
       </c>
     </row>
     <row r="194">
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>72.73178100585938</v>
+        <v>72.73178863525391</v>
       </c>
     </row>
     <row r="195">
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>72.34952545166016</v>
+        <v>72.34951782226562</v>
       </c>
     </row>
     <row r="196">
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>72.48993682861328</v>
+        <v>72.48995208740234</v>
       </c>
     </row>
     <row r="197">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>72.60697937011719</v>
+        <v>72.60696411132812</v>
       </c>
     </row>
     <row r="198">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>72.57576751708984</v>
+        <v>72.57575988769531</v>
       </c>
     </row>
     <row r="199">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>72.60697937011719</v>
+        <v>72.60696411132812</v>
       </c>
     </row>
     <row r="200">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>72.70056915283203</v>
+        <v>72.70059204101562</v>
       </c>
     </row>
     <row r="201">
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>73.7459716796875</v>
+        <v>73.74595642089844</v>
       </c>
     </row>
     <row r="204">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>74.30765533447266</v>
+        <v>74.30764770507812</v>
       </c>
     </row>
     <row r="205">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>74.25304412841797</v>
+        <v>74.25305938720703</v>
       </c>
     </row>
     <row r="207">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>74.06581115722656</v>
+        <v>74.06580352783203</v>
       </c>
     </row>
     <row r="208">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>73.43389129638672</v>
+        <v>73.43390655517578</v>
       </c>
     </row>
     <row r="209">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>73.43389129638672</v>
+        <v>73.43390655517578</v>
       </c>
     </row>
     <row r="211">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>73.69914245605469</v>
+        <v>73.69915008544922</v>
       </c>
     </row>
     <row r="212">
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>73.55091857910156</v>
+        <v>73.55092620849609</v>
       </c>
     </row>
     <row r="214">
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>71.79563140869141</v>
+        <v>71.79562377929688</v>
       </c>
     </row>
     <row r="216">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>71.95167541503906</v>
+        <v>71.95165252685547</v>
       </c>
     </row>
     <row r="217">
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>71.23392486572266</v>
+        <v>71.23394012451172</v>
       </c>
     </row>
     <row r="218">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>71.21832275390625</v>
+        <v>71.21834564208984</v>
       </c>
     </row>
     <row r="220">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>71.88144683837891</v>
+        <v>71.88143157958984</v>
       </c>
     </row>
     <row r="223">
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>72.27149963378906</v>
+        <v>72.27152252197266</v>
       </c>
     </row>
     <row r="224">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>72.62255859375</v>
+        <v>72.62256622314453</v>
       </c>
     </row>
     <row r="225">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>72.74739074707031</v>
+        <v>72.74738311767578</v>
       </c>
     </row>
     <row r="226">
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>71.68642425537109</v>
+        <v>71.68640899658203</v>
       </c>
     </row>
     <row r="228">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>71.42116546630859</v>
+        <v>71.42118072509766</v>
       </c>
     </row>
     <row r="229">
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>72.59915924072266</v>
+        <v>72.59914398193359</v>
       </c>
     </row>
     <row r="231">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>72.60697937011719</v>
+        <v>72.60696411132812</v>
       </c>
     </row>
     <row r="233">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>71.50697326660156</v>
+        <v>71.50698852539062</v>
       </c>
     </row>
     <row r="234">
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>71.96725463867188</v>
+        <v>71.96726226806641</v>
       </c>
     </row>
     <row r="235">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>72.26369476318359</v>
+        <v>72.26370239257812</v>
       </c>
     </row>
     <row r="236">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>72.30270385742188</v>
+        <v>72.30271911621094</v>
       </c>
     </row>
     <row r="237">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>72.45094299316406</v>
+        <v>72.45092010498047</v>
       </c>
     </row>
     <row r="238">
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>72.59135437011719</v>
+        <v>72.59136199951172</v>
       </c>
     </row>
     <row r="239">
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>72.17008972167969</v>
+        <v>72.17010498046875</v>
       </c>
     </row>
     <row r="240">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>71.436767578125</v>
+        <v>71.43675994873047</v>
       </c>
     </row>
     <row r="241">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>70.46941375732422</v>
+        <v>70.46940612792969</v>
       </c>
     </row>
     <row r="242">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>70.48500823974609</v>
+        <v>70.48501586914062</v>
       </c>
     </row>
     <row r="243">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>71.17826080322266</v>
+        <v>71.17828369140625</v>
       </c>
     </row>
     <row r="246">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>71.80908966064453</v>
+        <v>71.80908203125</v>
       </c>
     </row>
     <row r="247">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>72.20334625244141</v>
+        <v>72.20333099365234</v>
       </c>
     </row>
     <row r="248">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>71.84064483642578</v>
+        <v>71.84062957763672</v>
       </c>
     </row>
     <row r="249">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>72.02985382080078</v>
+        <v>72.02988433837891</v>
       </c>
     </row>
     <row r="250">
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>72.57392883300781</v>
+        <v>72.57394409179688</v>
       </c>
     </row>
     <row r="252">
@@ -2945,7 +2945,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>73.16532135009766</v>
+        <v>73.16529846191406</v>
       </c>
     </row>
     <row r="254">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>72.30583953857422</v>
+        <v>72.30584716796875</v>
       </c>
     </row>
     <row r="255">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>72.84201812744141</v>
+        <v>72.842041015625</v>
       </c>
     </row>
     <row r="257">
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>72.02985382080078</v>
+        <v>72.02988433837891</v>
       </c>
     </row>
     <row r="258">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>72.21122741699219</v>
+        <v>72.21121978759766</v>
       </c>
     </row>
     <row r="260">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>73.36243438720703</v>
+        <v>73.36241912841797</v>
       </c>
     </row>
     <row r="263">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>74.02476501464844</v>
+        <v>74.02477264404297</v>
       </c>
     </row>
     <row r="264">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>74.61616516113281</v>
+        <v>74.61613464355469</v>
       </c>
     </row>
     <row r="265">
@@ -3065,7 +3065,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>74.68712615966797</v>
+        <v>74.6871337890625</v>
       </c>
     </row>
     <row r="266">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>75.39678192138672</v>
+        <v>75.39675903320312</v>
       </c>
     </row>
     <row r="267">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>74.89212799072266</v>
+        <v>74.89214324951172</v>
       </c>
     </row>
     <row r="268">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>75.52294158935547</v>
+        <v>75.52293395996094</v>
       </c>
     </row>
     <row r="269">
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>74.90001678466797</v>
+        <v>74.90003204345703</v>
       </c>
     </row>
     <row r="271">
@@ -3125,7 +3125,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>75.19965362548828</v>
+        <v>75.19964599609375</v>
       </c>
     </row>
     <row r="272">
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>74.92367553710938</v>
+        <v>74.92366790771484</v>
       </c>
     </row>
     <row r="273">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>74.97886657714844</v>
+        <v>74.97887420654297</v>
       </c>
     </row>
     <row r="274">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>74.06421661376953</v>
+        <v>74.06420135498047</v>
       </c>
     </row>
     <row r="275">
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>74.30863952636719</v>
+        <v>74.30864715576172</v>
       </c>
     </row>
     <row r="276">
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>75.07347869873047</v>
+        <v>75.073486328125</v>
       </c>
     </row>
     <row r="277">
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>75.37311553955078</v>
+        <v>75.37310028076172</v>
       </c>
     </row>
     <row r="279">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>76.20104217529297</v>
+        <v>76.20106506347656</v>
       </c>
     </row>
     <row r="281">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>77.2340087890625</v>
+        <v>77.23401641845703</v>
       </c>
     </row>
     <row r="283">
@@ -3245,7 +3245,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>77.69922637939453</v>
+        <v>77.69921875</v>
       </c>
     </row>
     <row r="284">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>78.41674041748047</v>
+        <v>78.416748046875</v>
       </c>
     </row>
     <row r="286">
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>77.36015319824219</v>
+        <v>77.36013031005859</v>
       </c>
     </row>
     <row r="287">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>78.28270721435547</v>
+        <v>78.28269195556641</v>
       </c>
     </row>
     <row r="288">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>78.51139068603516</v>
+        <v>78.51138305664062</v>
       </c>
     </row>
     <row r="289">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>77.43900299072266</v>
+        <v>77.43901062011719</v>
       </c>
     </row>
     <row r="290">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>74.52942657470703</v>
+        <v>74.5294189453125</v>
       </c>
     </row>
     <row r="292">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>68.86009216308594</v>
+        <v>68.86006927490234</v>
       </c>
     </row>
     <row r="294">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>71.80120849609375</v>
+        <v>71.80119323730469</v>
       </c>
     </row>
     <row r="295">
@@ -3365,7 +3365,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>71.6356201171875</v>
+        <v>71.63560485839844</v>
       </c>
     </row>
     <row r="296">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>74.34017944335938</v>
+        <v>74.34016418457031</v>
       </c>
     </row>
     <row r="297">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>71.49368286132812</v>
+        <v>71.49369049072266</v>
       </c>
     </row>
     <row r="299">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>65.98202514648438</v>
+        <v>65.98204040527344</v>
       </c>
     </row>
     <row r="300">
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>68.76967620849609</v>
+        <v>68.76971435546875</v>
       </c>
     </row>
     <row r="301">
@@ -3425,7 +3425,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>64.63746643066406</v>
+        <v>64.63745880126953</v>
       </c>
     </row>
     <row r="302">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>58.08949279785156</v>
+        <v>58.0894889831543</v>
       </c>
     </row>
     <row r="303">
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>63.15940856933594</v>
+        <v>63.1594123840332</v>
       </c>
     </row>
     <row r="304">
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>51.96268081665039</v>
+        <v>51.96268463134766</v>
       </c>
     </row>
     <row r="305">
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>54.96648406982422</v>
+        <v>54.96648788452148</v>
       </c>
     </row>
     <row r="306">
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="B308" t="n">
-        <v>47.42519378662109</v>
+        <v>47.42518615722656</v>
       </c>
     </row>
     <row r="309">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>45.22397994995117</v>
+        <v>45.22397613525391</v>
       </c>
     </row>
     <row r="310">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>49.29263305664062</v>
+        <v>49.29263687133789</v>
       </c>
     </row>
     <row r="311">
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>55.61017608642578</v>
+        <v>55.61016845703125</v>
       </c>
     </row>
     <row r="313">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>55.66579055786133</v>
+        <v>55.66579437255859</v>
       </c>
     </row>
     <row r="314">
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>56.88162612915039</v>
+        <v>56.88161087036133</v>
       </c>
     </row>
     <row r="315">
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>55.50685882568359</v>
+        <v>55.50685119628906</v>
       </c>
     </row>
     <row r="316">
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>52.03419876098633</v>
+        <v>52.03420257568359</v>
       </c>
     </row>
     <row r="318">
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>51.27926635742188</v>
+        <v>51.27928161621094</v>
       </c>
     </row>
     <row r="319">
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>55.0777473449707</v>
+        <v>55.07773590087891</v>
       </c>
     </row>
     <row r="320">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>55.58631896972656</v>
+        <v>55.5863151550293</v>
       </c>
     </row>
     <row r="321">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>59.37685012817383</v>
+        <v>59.37682342529297</v>
       </c>
     </row>
     <row r="322">
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>62.70645523071289</v>
+        <v>62.70647048950195</v>
       </c>
     </row>
     <row r="323">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>60.06819152832031</v>
+        <v>60.06817626953125</v>
       </c>
     </row>
     <row r="324">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>61.75285720825195</v>
+        <v>61.75287628173828</v>
       </c>
     </row>
     <row r="325">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>59.3053092956543</v>
+        <v>59.30532455444336</v>
       </c>
     </row>
     <row r="326">
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>58.62984848022461</v>
+        <v>58.62985992431641</v>
       </c>
     </row>
     <row r="327">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>60.48141479492188</v>
+        <v>60.48142242431641</v>
       </c>
     </row>
     <row r="328">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>58.23255157470703</v>
+        <v>58.23252105712891</v>
       </c>
     </row>
     <row r="329">
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>57.17562866210938</v>
+        <v>57.17563629150391</v>
       </c>
     </row>
     <row r="330">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>57.56502151489258</v>
+        <v>57.56500625610352</v>
       </c>
     </row>
     <row r="332">
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>59.79005813598633</v>
+        <v>59.7900505065918</v>
       </c>
     </row>
     <row r="334">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>60.28275680541992</v>
+        <v>60.28273773193359</v>
       </c>
     </row>
     <row r="335">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>61.18867492675781</v>
+        <v>61.18865585327148</v>
       </c>
     </row>
     <row r="336">
@@ -3775,7 +3775,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>60.48141479492188</v>
+        <v>60.48142242431641</v>
       </c>
     </row>
     <row r="337">
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>58.43914031982422</v>
+        <v>58.43914794921875</v>
       </c>
     </row>
     <row r="338">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>58.15306854248047</v>
+        <v>58.15307235717773</v>
       </c>
     </row>
     <row r="339">
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>58.43914031982422</v>
+        <v>58.43914794921875</v>
       </c>
     </row>
     <row r="340">
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>58.20869827270508</v>
+        <v>58.20868682861328</v>
       </c>
     </row>
     <row r="342">
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>59.59140396118164</v>
+        <v>59.59139633178711</v>
       </c>
     </row>
     <row r="343">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>58.7252311706543</v>
+        <v>58.72522735595703</v>
       </c>
     </row>
     <row r="344">
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>56.05516815185547</v>
+        <v>56.0551643371582</v>
       </c>
     </row>
     <row r="345">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>54.6963005065918</v>
+        <v>54.69631195068359</v>
       </c>
     </row>
     <row r="346">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>54.88700485229492</v>
+        <v>54.88702774047852</v>
       </c>
     </row>
     <row r="347">
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>54.67246246337891</v>
+        <v>54.67246627807617</v>
       </c>
     </row>
     <row r="348">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>57.90671920776367</v>
+        <v>57.90673446655273</v>
       </c>
     </row>
     <row r="349">
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>57.12797546386719</v>
+        <v>57.12795257568359</v>
       </c>
     </row>
     <row r="350">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>57.63654708862305</v>
+        <v>57.63653564453125</v>
       </c>
     </row>
     <row r="351">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>57.68420791625977</v>
+        <v>57.68421173095703</v>
       </c>
     </row>
     <row r="352">
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>58.46298599243164</v>
+        <v>58.46299743652344</v>
       </c>
     </row>
     <row r="353">
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>60.64827728271484</v>
+        <v>60.64829254150391</v>
       </c>
     </row>
     <row r="354">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>61.85618209838867</v>
+        <v>61.85617446899414</v>
       </c>
     </row>
     <row r="355">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>62.15019989013672</v>
+        <v>62.15018844604492</v>
       </c>
     </row>
     <row r="356">
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>61.53034973144531</v>
+        <v>61.53036117553711</v>
       </c>
     </row>
     <row r="357">
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>63.46138763427734</v>
+        <v>63.46139144897461</v>
       </c>
     </row>
     <row r="359">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>65.49570465087891</v>
+        <v>65.49569702148438</v>
       </c>
     </row>
     <row r="360">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>64.84408569335938</v>
+        <v>64.84407806396484</v>
       </c>
     </row>
     <row r="361">
@@ -4035,7 +4035,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>68.96837615966797</v>
+        <v>68.96836853027344</v>
       </c>
     </row>
     <row r="363">
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>67.82405853271484</v>
+        <v>67.82405090332031</v>
       </c>
     </row>
     <row r="364">
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>61.85618209838867</v>
+        <v>61.85617446899414</v>
       </c>
     </row>
     <row r="366">
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>64.07326507568359</v>
+        <v>64.07324981689453</v>
       </c>
     </row>
     <row r="367">
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B367" t="n">
-        <v>64.97917175292969</v>
+        <v>64.97918701171875</v>
       </c>
     </row>
     <row r="368">
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>66.25859069824219</v>
+        <v>66.25856781005859</v>
       </c>
     </row>
     <row r="369">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>65.29703521728516</v>
+        <v>65.29704284667969</v>
       </c>
     </row>
     <row r="370">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>64.58184051513672</v>
+        <v>64.58184814453125</v>
       </c>
     </row>
     <row r="371">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>63.64413452148438</v>
+        <v>63.64416122436523</v>
       </c>
     </row>
     <row r="372">
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>63.58057403564453</v>
+        <v>63.58058929443359</v>
       </c>
     </row>
     <row r="373">
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>63.3183479309082</v>
+        <v>63.31834030151367</v>
       </c>
     </row>
     <row r="374">
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>61.51447296142578</v>
+        <v>61.51448059082031</v>
       </c>
     </row>
     <row r="375">
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>62.30012893676758</v>
+        <v>62.30014038085938</v>
       </c>
     </row>
     <row r="376">
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>62.28410339355469</v>
+        <v>62.28408813476562</v>
       </c>
     </row>
     <row r="378">
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>63.02241897583008</v>
+        <v>63.02242279052734</v>
       </c>
     </row>
     <row r="379">
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>64.47498321533203</v>
+        <v>64.47499847412109</v>
       </c>
     </row>
     <row r="380">
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>64.29042053222656</v>
+        <v>64.29041290283203</v>
       </c>
     </row>
     <row r="381">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>64.25830841064453</v>
+        <v>64.25833129882812</v>
       </c>
     </row>
     <row r="382">
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>62.98230361938477</v>
+        <v>62.9822998046875</v>
       </c>
     </row>
     <row r="383">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>62.89400863647461</v>
+        <v>62.89401626586914</v>
       </c>
     </row>
     <row r="384">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>62.50078201293945</v>
+        <v>62.50077056884766</v>
       </c>
     </row>
     <row r="385">
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="B385" t="n">
-        <v>62.69337844848633</v>
+        <v>62.69340896606445</v>
       </c>
     </row>
     <row r="386">
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>61.947021484375</v>
+        <v>61.94704055786133</v>
       </c>
     </row>
     <row r="387">
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>62.46869277954102</v>
+        <v>62.46867752075195</v>
       </c>
     </row>
     <row r="388">
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="B388" t="n">
-        <v>63.07859039306641</v>
+        <v>63.07857513427734</v>
       </c>
     </row>
     <row r="389">
@@ -4305,7 +4305,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>62.32422256469727</v>
+        <v>62.32421493530273</v>
       </c>
     </row>
     <row r="390">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>63.134765625</v>
+        <v>63.13478469848633</v>
       </c>
     </row>
     <row r="391">
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>62.53286743164062</v>
+        <v>62.53288269042969</v>
       </c>
     </row>
     <row r="393">
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>63.48788070678711</v>
+        <v>63.48787307739258</v>
       </c>
     </row>
     <row r="394">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="B394" t="n">
-        <v>63.22305297851562</v>
+        <v>63.22304916381836</v>
       </c>
     </row>
     <row r="395">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>62.75759124755859</v>
+        <v>62.7575798034668</v>
       </c>
     </row>
     <row r="396">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>63.35145950317383</v>
+        <v>63.35145568847656</v>
       </c>
     </row>
     <row r="397">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>64.61141967773438</v>
+        <v>64.61142730712891</v>
       </c>
     </row>
     <row r="398">
@@ -4395,7 +4395,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>65.86335754394531</v>
+        <v>65.86336517333984</v>
       </c>
     </row>
     <row r="399">
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>65.43801879882812</v>
+        <v>65.43799591064453</v>
       </c>
     </row>
     <row r="400">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="B400" t="n">
-        <v>65.31764984130859</v>
+        <v>65.31763458251953</v>
       </c>
     </row>
     <row r="401">
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>64.45090484619141</v>
+        <v>64.45092010498047</v>
       </c>
     </row>
     <row r="402">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="B402" t="n">
-        <v>65.41395568847656</v>
+        <v>65.4139404296875</v>
       </c>
     </row>
     <row r="403">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="B403" t="n">
-        <v>65.08492279052734</v>
+        <v>65.08490753173828</v>
       </c>
     </row>
     <row r="404">
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>66.12017822265625</v>
+        <v>66.12017059326172</v>
       </c>
     </row>
     <row r="406">
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>66.22452545166016</v>
+        <v>66.22449493408203</v>
       </c>
     </row>
     <row r="407">
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>65.26950836181641</v>
+        <v>65.26951599121094</v>
       </c>
     </row>
     <row r="408">
@@ -4495,7 +4495,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>65.92756652832031</v>
+        <v>65.92758178710938</v>
       </c>
     </row>
     <row r="409">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>65.12503051757812</v>
+        <v>65.12504577636719</v>
       </c>
     </row>
     <row r="411">
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>65.65470123291016</v>
+        <v>65.65469360351562</v>
       </c>
     </row>
     <row r="412">
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>64.19411468505859</v>
+        <v>64.19412231445312</v>
       </c>
     </row>
     <row r="414">
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>64.80403137207031</v>
+        <v>64.80403900146484</v>
       </c>
     </row>
     <row r="415">
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>65.32566833496094</v>
+        <v>65.32568359375</v>
       </c>
     </row>
     <row r="417">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>65.49420166015625</v>
+        <v>65.49420928955078</v>
       </c>
     </row>
     <row r="418">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>64.89231872558594</v>
+        <v>64.89229583740234</v>
       </c>
     </row>
     <row r="419">
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>65.84733581542969</v>
+        <v>65.84729766845703</v>
       </c>
     </row>
     <row r="420">
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>66.28068542480469</v>
+        <v>66.28067016601562</v>
       </c>
     </row>
     <row r="421">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="B421" t="n">
-        <v>65.60654449462891</v>
+        <v>65.60655212402344</v>
       </c>
     </row>
     <row r="422">
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>65.65470123291016</v>
+        <v>65.65469360351562</v>
       </c>
     </row>
     <row r="423">
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>66.07201385498047</v>
+        <v>66.07200622558594</v>
       </c>
     </row>
     <row r="425">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>64.92440795898438</v>
+        <v>64.92441558837891</v>
       </c>
     </row>
     <row r="427">
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>65.56642913818359</v>
+        <v>65.56642150878906</v>
       </c>
     </row>
     <row r="428">
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="B429" t="n">
-        <v>64.40276336669922</v>
+        <v>64.40275573730469</v>
       </c>
     </row>
     <row r="430">
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>65.97572326660156</v>
+        <v>65.97571563720703</v>
       </c>
     </row>
     <row r="431">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>66.77021026611328</v>
+        <v>66.77020263671875</v>
       </c>
     </row>
     <row r="432">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>67.12334442138672</v>
+        <v>67.12332916259766</v>
       </c>
     </row>
     <row r="433">
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>64.33053588867188</v>
+        <v>64.33055114746094</v>
       </c>
     </row>
     <row r="435">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>62.39644622802734</v>
+        <v>62.39645385742188</v>
       </c>
     </row>
     <row r="436">
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="B436" t="n">
-        <v>63.14279937744141</v>
+        <v>63.14279556274414</v>
       </c>
     </row>
     <row r="437">
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>61.24079513549805</v>
+        <v>61.24082183837891</v>
       </c>
     </row>
     <row r="438">
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>61.56984710693359</v>
+        <v>61.56984329223633</v>
       </c>
     </row>
     <row r="439">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>62.83956909179688</v>
+        <v>62.83959197998047</v>
       </c>
     </row>
     <row r="440">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>64.12548065185547</v>
+        <v>64.12547302246094</v>
       </c>
     </row>
     <row r="441">
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="B441" t="n">
-        <v>63.66450881958008</v>
+        <v>63.66448593139648</v>
       </c>
     </row>
     <row r="442">
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>63.85860443115234</v>
+        <v>63.85858917236328</v>
       </c>
     </row>
     <row r="443">
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>65.13642120361328</v>
+        <v>65.13641357421875</v>
       </c>
     </row>
     <row r="444">
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>66.26059722900391</v>
+        <v>66.26058197021484</v>
       </c>
     </row>
     <row r="445">
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>66.64069366455078</v>
+        <v>66.64067840576172</v>
       </c>
     </row>
     <row r="446">
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>66.20395660400391</v>
+        <v>66.20394897460938</v>
       </c>
     </row>
     <row r="447">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>66.30101776123047</v>
+        <v>66.30101013183594</v>
       </c>
     </row>
     <row r="448">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>67.40901184082031</v>
+        <v>67.40898132324219</v>
       </c>
     </row>
     <row r="449">
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="B449" t="n">
-        <v>67.14211273193359</v>
+        <v>67.14209747314453</v>
       </c>
     </row>
     <row r="450">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>67.45750427246094</v>
+        <v>67.45751953125</v>
       </c>
     </row>
     <row r="451">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="B451" t="n">
-        <v>66.30101776123047</v>
+        <v>66.30101013183594</v>
       </c>
     </row>
     <row r="452">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="B454" t="n">
-        <v>65.36288452148438</v>
+        <v>65.36285400390625</v>
       </c>
     </row>
     <row r="455">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>64.34384918212891</v>
+        <v>64.34384155273438</v>
       </c>
     </row>
     <row r="456">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>64.80484771728516</v>
+        <v>64.80485534667969</v>
       </c>
     </row>
     <row r="457">
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>64.61072540283203</v>
+        <v>64.61073303222656</v>
       </c>
     </row>
     <row r="458">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>64.60264587402344</v>
+        <v>64.60263824462891</v>
       </c>
     </row>
     <row r="459">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>64.9908447265625</v>
+        <v>64.99085235595703</v>
       </c>
     </row>
     <row r="460">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>64.06078338623047</v>
+        <v>64.060791015625</v>
       </c>
     </row>
     <row r="461">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>63.03369140625</v>
+        <v>63.03368759155273</v>
       </c>
     </row>
     <row r="462">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>61.52941513061523</v>
+        <v>61.5294075012207</v>
       </c>
     </row>
     <row r="463">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>62.35433578491211</v>
+        <v>62.35433197021484</v>
       </c>
     </row>
     <row r="464">
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>61.94187927246094</v>
+        <v>61.94186782836914</v>
       </c>
     </row>
     <row r="465">
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>63.42188262939453</v>
+        <v>63.421875</v>
       </c>
     </row>
     <row r="466">
@@ -5075,7 +5075,7 @@
         </is>
       </c>
       <c r="B466" t="n">
-        <v>64.64306640625</v>
+        <v>64.64308929443359</v>
       </c>
     </row>
     <row r="467">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="B467" t="n">
-        <v>64.75630950927734</v>
+        <v>64.75630187988281</v>
       </c>
     </row>
     <row r="468">
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="B468" t="n">
-        <v>65.06362915039062</v>
+        <v>65.06361389160156</v>
       </c>
     </row>
     <row r="469">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>66.90756988525391</v>
+        <v>66.90757751464844</v>
       </c>
     </row>
     <row r="471">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>67.88614654541016</v>
+        <v>67.88616180419922</v>
       </c>
     </row>
     <row r="472">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>69.05075836181641</v>
+        <v>69.05074310302734</v>
       </c>
     </row>
     <row r="475">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>69.8271484375</v>
+        <v>69.82714080810547</v>
       </c>
     </row>
     <row r="476">
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>69.89185333251953</v>
+        <v>69.891845703125</v>
       </c>
     </row>
     <row r="477">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>68.53314208984375</v>
+        <v>68.53314971923828</v>
       </c>
     </row>
     <row r="478">
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="B478" t="n">
-        <v>68.800048828125</v>
+        <v>68.80004119873047</v>
       </c>
     </row>
     <row r="479">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>68.42800903320312</v>
+        <v>68.42801666259766</v>
       </c>
     </row>
     <row r="480">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>68.55741882324219</v>
+        <v>68.55742645263672</v>
       </c>
     </row>
     <row r="481">
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>68.92134094238281</v>
+        <v>68.92135620117188</v>
       </c>
     </row>
     <row r="482">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>68.9617919921875</v>
+        <v>68.96177673339844</v>
       </c>
     </row>
     <row r="483">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>68.65444183349609</v>
+        <v>68.65446472167969</v>
       </c>
     </row>
     <row r="484">
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>68.80814361572266</v>
+        <v>68.80813598632812</v>
       </c>
     </row>
     <row r="486">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>68.26626586914062</v>
+        <v>68.26627349853516</v>
       </c>
     </row>
     <row r="487">
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>68.84048461914062</v>
+        <v>68.84047698974609</v>
       </c>
     </row>
     <row r="488">
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>69.89185333251953</v>
+        <v>69.891845703125</v>
       </c>
     </row>
     <row r="489">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>69.28530120849609</v>
+        <v>69.2852783203125</v>
       </c>
     </row>
     <row r="490">
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>69.04266357421875</v>
+        <v>69.04267120361328</v>
       </c>
     </row>
     <row r="491">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>68.61402893066406</v>
+        <v>68.614013671875</v>
       </c>
     </row>
     <row r="492">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>68.31480407714844</v>
+        <v>68.31477355957031</v>
       </c>
     </row>
     <row r="493">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>67.95084381103516</v>
+        <v>67.95085144042969</v>
       </c>
     </row>
     <row r="495">
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>69.42278289794922</v>
+        <v>69.42276000976562</v>
       </c>
     </row>
     <row r="497">
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>68.29862213134766</v>
+        <v>68.29860687255859</v>
       </c>
     </row>
     <row r="500">
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>68.77577972412109</v>
+        <v>68.77577209472656</v>
       </c>
     </row>
     <row r="501">
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>68.33095550537109</v>
+        <v>68.33096313476562</v>
       </c>
     </row>
     <row r="502">
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>68.92919921875</v>
+        <v>68.92920684814453</v>
       </c>
     </row>
     <row r="503">
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>69.340087890625</v>
+        <v>69.34008026123047</v>
       </c>
     </row>
     <row r="504">
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>68.7484130859375</v>
+        <v>68.74844360351562</v>
       </c>
     </row>
     <row r="505">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>69.12644195556641</v>
+        <v>69.12644958496094</v>
       </c>
     </row>
     <row r="506">
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>67.52399444580078</v>
+        <v>67.52400970458984</v>
       </c>
     </row>
     <row r="508">
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>67.62259674072266</v>
+        <v>67.62260437011719</v>
       </c>
     </row>
     <row r="509">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>67.7376708984375</v>
+        <v>67.73765563964844</v>
       </c>
     </row>
     <row r="510">
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>67.60617065429688</v>
+        <v>67.60616302490234</v>
       </c>
     </row>
     <row r="511">
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>68.26358795166016</v>
+        <v>68.26357269287109</v>
       </c>
     </row>
     <row r="512">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>67.35963439941406</v>
+        <v>67.35964965820312</v>
       </c>
     </row>
     <row r="513">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>68.33753204345703</v>
+        <v>68.33753967285156</v>
       </c>
     </row>
     <row r="515">
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>69.52908325195312</v>
+        <v>69.52909088134766</v>
       </c>
     </row>
     <row r="517">
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>69.33184814453125</v>
+        <v>69.33188629150391</v>
       </c>
     </row>
     <row r="518">
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>70.65489196777344</v>
+        <v>70.65489959716797</v>
       </c>
     </row>
     <row r="519">
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>70.31798553466797</v>
+        <v>70.31796264648438</v>
       </c>
     </row>
     <row r="520">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>71.01647186279297</v>
+        <v>71.0164794921875</v>
       </c>
     </row>
     <row r="522">
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>70.25224304199219</v>
+        <v>70.25223541259766</v>
       </c>
     </row>
     <row r="524">
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>70.63024139404297</v>
+        <v>70.63023376464844</v>
       </c>
     </row>
     <row r="525">
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>69.81672668457031</v>
+        <v>69.81671142578125</v>
       </c>
     </row>
     <row r="526">
@@ -5675,7 +5675,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>71.41090393066406</v>
+        <v>71.41091918945312</v>
       </c>
     </row>
     <row r="527">
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>71.65744781494141</v>
+        <v>71.65746307373047</v>
       </c>
     </row>
     <row r="529">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>72.15049743652344</v>
+        <v>72.15050506591797</v>
       </c>
     </row>
     <row r="530">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>72.40525817871094</v>
+        <v>72.40524291992188</v>
       </c>
     </row>
     <row r="531">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="B531" t="n">
-        <v>72.7996826171875</v>
+        <v>72.79966735839844</v>
       </c>
     </row>
     <row r="532">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="B532" t="n">
-        <v>73.054443359375</v>
+        <v>73.05443572998047</v>
       </c>
     </row>
     <row r="533">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="B534" t="n">
-        <v>73.60502624511719</v>
+        <v>73.60503387451172</v>
       </c>
     </row>
     <row r="535">
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="B535" t="n">
-        <v>73.62146759033203</v>
+        <v>73.62144470214844</v>
       </c>
     </row>
     <row r="536">
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>73.054443359375</v>
+        <v>73.05443572998047</v>
       </c>
     </row>
     <row r="537">
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="B537" t="n">
-        <v>72.96404266357422</v>
+        <v>72.96403503417969</v>
       </c>
     </row>
     <row r="538">
@@ -5795,7 +5795,7 @@
         </is>
       </c>
       <c r="B538" t="n">
-        <v>72.65177917480469</v>
+        <v>72.65179443359375</v>
       </c>
     </row>
     <row r="539">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B540" t="n">
-        <v>73.67898559570312</v>
+        <v>73.67897033691406</v>
       </c>
     </row>
     <row r="541">
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="B541" t="n">
-        <v>74.13915252685547</v>
+        <v>74.13916015625</v>
       </c>
     </row>
     <row r="542">
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B542" t="n">
-        <v>74.70619201660156</v>
+        <v>74.7061767578125</v>
       </c>
     </row>
     <row r="543">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="B544" t="n">
-        <v>72.20803070068359</v>
+        <v>72.20803833007812</v>
       </c>
     </row>
     <row r="545">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B546" t="n">
-        <v>71.83001708984375</v>
+        <v>71.83002471923828</v>
       </c>
     </row>
     <row r="547">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="B547" t="n">
-        <v>71.41913604736328</v>
+        <v>71.41915893554688</v>
       </c>
     </row>
     <row r="548">
@@ -5895,7 +5895,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>70.6055908203125</v>
+        <v>70.60559844970703</v>
       </c>
     </row>
     <row r="549">
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="B549" t="n">
-        <v>71.37802886962891</v>
+        <v>71.37804412841797</v>
       </c>
     </row>
     <row r="550">
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>73.19411468505859</v>
+        <v>73.19415283203125</v>
       </c>
     </row>
     <row r="553">
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="B557" t="n">
-        <v>76.16069030761719</v>
+        <v>76.16068267822266</v>
       </c>
     </row>
     <row r="558">
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="B558" t="n">
-        <v>75.38822937011719</v>
+        <v>75.38824462890625</v>
       </c>
     </row>
     <row r="559">
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="B559" t="n">
-        <v>74.36104583740234</v>
+        <v>74.36103057861328</v>
       </c>
     </row>
     <row r="560">
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="B560" t="n">
-        <v>74.886962890625</v>
+        <v>74.88694763183594</v>
       </c>
     </row>
     <row r="561">
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="B561" t="n">
-        <v>74.78013610839844</v>
+        <v>74.78012847900391</v>
       </c>
     </row>
     <row r="562">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="B562" t="n">
-        <v>74.36104583740234</v>
+        <v>74.36103057861328</v>
       </c>
     </row>
     <row r="563">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>75.1181640625</v>
+        <v>75.11817932128906</v>
       </c>
     </row>
     <row r="564">
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="B565" t="n">
-        <v>76.29190826416016</v>
+        <v>76.29188537597656</v>
       </c>
     </row>
     <row r="566">
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>76.39108276367188</v>
+        <v>76.39109039306641</v>
       </c>
     </row>
     <row r="567">
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>75.92821502685547</v>
+        <v>75.92819976806641</v>
       </c>
     </row>
     <row r="568">
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="B568" t="n">
-        <v>77.30855560302734</v>
+        <v>77.30857849121094</v>
       </c>
     </row>
     <row r="569">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>77.60610961914062</v>
+        <v>77.60612487792969</v>
       </c>
     </row>
     <row r="570">
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>77.80451965332031</v>
+        <v>77.80451202392578</v>
       </c>
     </row>
     <row r="571">
@@ -6135,7 +6135,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>77.57308197021484</v>
+        <v>77.57307434082031</v>
       </c>
     </row>
     <row r="573">
@@ -6165,7 +6165,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>78.32524108886719</v>
+        <v>78.32523345947266</v>
       </c>
     </row>
     <row r="576">
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>77.91195678710938</v>
+        <v>77.91194915771484</v>
       </c>
     </row>
     <row r="577">
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="B577" t="n">
-        <v>79.27579498291016</v>
+        <v>79.27578735351562</v>
       </c>
     </row>
     <row r="578">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>79.44935607910156</v>
+        <v>79.44937133789062</v>
       </c>
     </row>
     <row r="579">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>79.60642242431641</v>
+        <v>79.60639953613281</v>
       </c>
     </row>
     <row r="580">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="B581" t="n">
-        <v>80.78838348388672</v>
+        <v>80.78840637207031</v>
       </c>
     </row>
     <row r="582">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="B582" t="n">
-        <v>80.35033416748047</v>
+        <v>80.35032653808594</v>
       </c>
     </row>
     <row r="583">
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="B583" t="n">
-        <v>80.82146453857422</v>
+        <v>80.82144927978516</v>
       </c>
     </row>
     <row r="584">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="B585" t="n">
-        <v>81.05290222167969</v>
+        <v>81.05290985107422</v>
       </c>
     </row>
     <row r="586">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="B586" t="n">
-        <v>80.87934112548828</v>
+        <v>80.87932586669922</v>
       </c>
     </row>
     <row r="587">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="B588" t="n">
-        <v>81.89599609375</v>
+        <v>81.89598083496094</v>
       </c>
     </row>
     <row r="589">
@@ -6305,7 +6305,7 @@
         </is>
       </c>
       <c r="B589" t="n">
-        <v>81.73894500732422</v>
+        <v>81.73893737792969</v>
       </c>
     </row>
     <row r="590">
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="B591" t="n">
-        <v>79.86266326904297</v>
+        <v>79.8626708984375</v>
       </c>
     </row>
     <row r="592">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="B592" t="n">
-        <v>80.30899810791016</v>
+        <v>80.30900573730469</v>
       </c>
     </row>
     <row r="593">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="B595" t="n">
-        <v>80.31724548339844</v>
+        <v>80.31725311279297</v>
       </c>
     </row>
     <row r="596">
@@ -6385,7 +6385,7 @@
         </is>
       </c>
       <c r="B597" t="n">
-        <v>79.30059051513672</v>
+        <v>79.30058288574219</v>
       </c>
     </row>
     <row r="598">
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="B598" t="n">
-        <v>80.24286651611328</v>
+        <v>80.24285888671875</v>
       </c>
     </row>
     <row r="599">
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>80.32551574707031</v>
+        <v>80.32553863525391</v>
       </c>
     </row>
     <row r="600">
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="B600" t="n">
-        <v>80.34205627441406</v>
+        <v>80.34206390380859</v>
       </c>
     </row>
     <row r="601">
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>80.98676300048828</v>
+        <v>80.98679351806641</v>
       </c>
     </row>
     <row r="603">
@@ -6445,7 +6445,7 @@
         </is>
       </c>
       <c r="B603" t="n">
-        <v>80.90411376953125</v>
+        <v>80.90412139892578</v>
       </c>
     </row>
     <row r="604">
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="B604" t="n">
-        <v>81.91253662109375</v>
+        <v>81.91252899169922</v>
       </c>
     </row>
     <row r="605">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>81.88774871826172</v>
+        <v>81.88774108886719</v>
       </c>
     </row>
     <row r="606">
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="B606" t="n">
-        <v>82.25142669677734</v>
+        <v>82.25143432617188</v>
       </c>
     </row>
     <row r="607">
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="B607" t="n">
-        <v>82.06131744384766</v>
+        <v>82.06129455566406</v>
       </c>
     </row>
     <row r="608">
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B608" t="n">
-        <v>82.55726623535156</v>
+        <v>82.55723571777344</v>
       </c>
     </row>
     <row r="609">
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="B610" t="n">
-        <v>85.02867126464844</v>
+        <v>85.0286865234375</v>
       </c>
     </row>
     <row r="611">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>84.71458435058594</v>
+        <v>84.71459197998047</v>
       </c>
     </row>
     <row r="612">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B612" t="n">
-        <v>84.75592803955078</v>
+        <v>84.75592041015625</v>
       </c>
     </row>
     <row r="613">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="B613" t="n">
-        <v>85.75606536865234</v>
+        <v>85.75605010986328</v>
       </c>
     </row>
     <row r="614">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="B614" t="n">
-        <v>86.46691131591797</v>
+        <v>86.4669189453125</v>
       </c>
     </row>
     <row r="615">
@@ -6565,7 +6565,7 @@
         </is>
       </c>
       <c r="B615" t="n">
-        <v>86.58261108398438</v>
+        <v>86.58261871337891</v>
       </c>
     </row>
     <row r="616">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="B616" t="n">
-        <v>87.20254516601562</v>
+        <v>87.20255279541016</v>
       </c>
     </row>
     <row r="617">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="B617" t="n">
-        <v>86.85537719726562</v>
+        <v>86.85538482666016</v>
       </c>
     </row>
     <row r="618">
@@ -6595,7 +6595,7 @@
         </is>
       </c>
       <c r="B618" t="n">
-        <v>87.19427490234375</v>
+        <v>87.19428253173828</v>
       </c>
     </row>
     <row r="619">
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="B620" t="n">
-        <v>85.69820404052734</v>
+        <v>85.69821166992188</v>
       </c>
     </row>
     <row r="621">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="B621" t="n">
-        <v>85.59074401855469</v>
+        <v>85.59073638916016</v>
       </c>
     </row>
     <row r="622">
@@ -6635,7 +6635,7 @@
         </is>
       </c>
       <c r="B622" t="n">
-        <v>84.13600158691406</v>
+        <v>84.13597869873047</v>
       </c>
     </row>
     <row r="623">
@@ -6645,7 +6645,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>85.87178039550781</v>
+        <v>85.87177276611328</v>
       </c>
     </row>
     <row r="624">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="B627" t="n">
-        <v>85.66708374023438</v>
+        <v>85.66706848144531</v>
       </c>
     </row>
     <row r="628">
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="B628" t="n">
-        <v>85.41732025146484</v>
+        <v>85.41733551025391</v>
       </c>
     </row>
     <row r="629">
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B629" t="n">
-        <v>85.18423461914062</v>
+        <v>85.18424987792969</v>
       </c>
     </row>
     <row r="630">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="B632" t="n">
-        <v>85.35906219482422</v>
+        <v>85.35904693603516</v>
       </c>
     </row>
     <row r="633">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="B633" t="n">
-        <v>85.98339080810547</v>
+        <v>85.9833984375</v>
       </c>
     </row>
     <row r="634">
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="B634" t="n">
-        <v>86.2830810546875</v>
+        <v>86.28306579589844</v>
       </c>
     </row>
     <row r="635">
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="B636" t="n">
-        <v>87.45682525634766</v>
+        <v>87.45680999755859</v>
       </c>
     </row>
     <row r="637">
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="B637" t="n">
-        <v>88.20603179931641</v>
+        <v>88.20601654052734</v>
       </c>
     </row>
     <row r="638">
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="B638" t="n">
-        <v>86.97402191162109</v>
+        <v>86.97400665283203</v>
       </c>
     </row>
     <row r="639">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="B639" t="n">
-        <v>87.58169555664062</v>
+        <v>87.58168792724609</v>
       </c>
     </row>
     <row r="640">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="B641" t="n">
-        <v>87.66492462158203</v>
+        <v>87.66493225097656</v>
       </c>
     </row>
     <row r="642">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="B642" t="n">
-        <v>86.06662750244141</v>
+        <v>86.06663513183594</v>
       </c>
     </row>
     <row r="643">
@@ -6845,7 +6845,7 @@
         </is>
       </c>
       <c r="B643" t="n">
-        <v>88.09782409667969</v>
+        <v>88.09781646728516</v>
       </c>
     </row>
     <row r="644">
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="B644" t="n">
-        <v>88.08950042724609</v>
+        <v>88.08948516845703</v>
       </c>
     </row>
     <row r="645">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="B647" t="n">
-        <v>88.15606689453125</v>
+        <v>88.15609741210938</v>
       </c>
     </row>
     <row r="648">
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="B648" t="n">
-        <v>88.65554809570312</v>
+        <v>88.65554046630859</v>
       </c>
     </row>
     <row r="649">
@@ -6905,7 +6905,7 @@
         </is>
       </c>
       <c r="B649" t="n">
-        <v>88.34754943847656</v>
+        <v>88.34752655029297</v>
       </c>
     </row>
     <row r="650">
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B650" t="n">
-        <v>88.36420440673828</v>
+        <v>88.36418151855469</v>
       </c>
     </row>
     <row r="651">
@@ -6925,7 +6925,7 @@
         </is>
       </c>
       <c r="B651" t="n">
-        <v>88.48075103759766</v>
+        <v>88.48073577880859</v>
       </c>
     </row>
     <row r="652">
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="B653" t="n">
-        <v>88.39748382568359</v>
+        <v>88.39749908447266</v>
       </c>
     </row>
     <row r="654">
@@ -6975,7 +6975,7 @@
         </is>
       </c>
       <c r="B656" t="n">
-        <v>88.99684143066406</v>
+        <v>88.99685668945312</v>
       </c>
     </row>
     <row r="657">
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="B658" t="n">
-        <v>87.68160247802734</v>
+        <v>87.68157958984375</v>
       </c>
     </row>
     <row r="659">
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="B660" t="n">
-        <v>88.38917541503906</v>
+        <v>88.38916015625</v>
       </c>
     </row>
     <row r="661">
@@ -7025,7 +7025,7 @@
         </is>
       </c>
       <c r="B661" t="n">
-        <v>88.87197113037109</v>
+        <v>88.87199401855469</v>
       </c>
     </row>
     <row r="662">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>88.76375579833984</v>
+        <v>88.76377105712891</v>
       </c>
     </row>
     <row r="663">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="B663" t="n">
-        <v>88.67218780517578</v>
+        <v>88.67220306396484</v>
       </c>
     </row>
     <row r="664">
@@ -7055,7 +7055,7 @@
         </is>
       </c>
       <c r="B664" t="n">
-        <v>87.86473846435547</v>
+        <v>87.86472320556641</v>
       </c>
     </row>
     <row r="665">
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="B666" t="n">
-        <v>88.73045349121094</v>
+        <v>88.73046875</v>
       </c>
     </row>
     <row r="667">
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="B667" t="n">
-        <v>88.56397247314453</v>
+        <v>88.56398010253906</v>
       </c>
     </row>
     <row r="668">
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="B668" t="n">
-        <v>88.17273712158203</v>
+        <v>88.1727294921875</v>
       </c>
     </row>
     <row r="669">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="B670" t="n">
-        <v>88.14776611328125</v>
+        <v>88.14775085449219</v>
       </c>
     </row>
     <row r="671">
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="B671" t="n">
-        <v>89.07176208496094</v>
+        <v>89.07177734375</v>
       </c>
     </row>
     <row r="672">
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="B672" t="n">
-        <v>89.96248626708984</v>
+        <v>89.96249389648438</v>
       </c>
     </row>
     <row r="673">
@@ -7145,7 +7145,7 @@
         </is>
       </c>
       <c r="B673" t="n">
-        <v>90.38705444335938</v>
+        <v>90.38703155517578</v>
       </c>
     </row>
     <row r="674">
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="B674" t="n">
-        <v>91.83548736572266</v>
+        <v>91.83550262451172</v>
       </c>
     </row>
     <row r="675">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="B675" t="n">
-        <v>92.31830596923828</v>
+        <v>92.31832122802734</v>
       </c>
     </row>
     <row r="676">
@@ -7185,7 +7185,7 @@
         </is>
       </c>
       <c r="B677" t="n">
-        <v>91.29440307617188</v>
+        <v>91.29439544677734</v>
       </c>
     </row>
     <row r="678">
@@ -7195,7 +7195,7 @@
         </is>
       </c>
       <c r="B678" t="n">
-        <v>91.75225830078125</v>
+        <v>91.75225067138672</v>
       </c>
     </row>
     <row r="679">
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="B680" t="n">
-        <v>88.57230377197266</v>
+        <v>88.57229614257812</v>
       </c>
     </row>
     <row r="681">
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="B681" t="n">
-        <v>89.17166900634766</v>
+        <v>89.17165374755859</v>
       </c>
     </row>
     <row r="682">
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="B682" t="n">
-        <v>89.01351165771484</v>
+        <v>89.01350402832031</v>
       </c>
     </row>
     <row r="683">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="B683" t="n">
-        <v>89.29652404785156</v>
+        <v>89.29653167724609</v>
       </c>
     </row>
     <row r="684">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>89.37145233154297</v>
+        <v>89.3714599609375</v>
       </c>
     </row>
     <row r="685">
@@ -7265,7 +7265,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>88.57230377197266</v>
+        <v>88.57229614257812</v>
       </c>
     </row>
     <row r="686">
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>88.03124237060547</v>
+        <v>88.03121185302734</v>
       </c>
     </row>
     <row r="687">
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>88.93024444580078</v>
+        <v>88.93026733398438</v>
       </c>
     </row>
     <row r="689">
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="B689" t="n">
-        <v>88.75542449951172</v>
+        <v>88.75543975830078</v>
       </c>
     </row>
     <row r="690">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="B690" t="n">
-        <v>87.80643463134766</v>
+        <v>87.80642700195312</v>
       </c>
     </row>
     <row r="691">
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="B691" t="n">
-        <v>86.62539672851562</v>
+        <v>86.62541198730469</v>
       </c>
     </row>
     <row r="692">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>86.03907775878906</v>
+        <v>86.03908538818359</v>
       </c>
     </row>
     <row r="693">
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>85.25173187255859</v>
+        <v>85.25173950195312</v>
       </c>
     </row>
     <row r="695">
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="B695" t="n">
-        <v>86.4578857421875</v>
+        <v>86.45787811279297</v>
       </c>
     </row>
     <row r="696">
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>86.47464752197266</v>
+        <v>86.47463226318359</v>
       </c>
     </row>
     <row r="697">
@@ -7385,7 +7385,7 @@
         </is>
       </c>
       <c r="B697" t="n">
-        <v>85.87994384765625</v>
+        <v>85.87993621826172</v>
       </c>
     </row>
     <row r="698">
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>86.7008056640625</v>
+        <v>86.70078277587891</v>
       </c>
     </row>
     <row r="699">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="B699" t="n">
-        <v>86.93533325195312</v>
+        <v>86.93532562255859</v>
       </c>
     </row>
     <row r="700">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="B700" t="n">
-        <v>86.11446380615234</v>
+        <v>86.11444854736328</v>
       </c>
     </row>
     <row r="701">
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>86.33223724365234</v>
+        <v>86.33225250244141</v>
       </c>
     </row>
     <row r="702">
@@ -7435,7 +7435,7 @@
         </is>
       </c>
       <c r="B702" t="n">
-        <v>87.46302795410156</v>
+        <v>87.46300506591797</v>
       </c>
     </row>
     <row r="703">
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="B703" t="n">
-        <v>88.09961700439453</v>
+        <v>88.09960174560547</v>
       </c>
     </row>
     <row r="704">
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="B704" t="n">
-        <v>89.17173767089844</v>
+        <v>89.17173004150391</v>
       </c>
     </row>
     <row r="705">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="B705" t="n">
-        <v>89.10471343994141</v>
+        <v>89.10472869873047</v>
       </c>
     </row>
     <row r="706">
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>89.33086395263672</v>
+        <v>89.33087921142578</v>
       </c>
     </row>
     <row r="707">
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>89.37275695800781</v>
+        <v>89.37274932861328</v>
       </c>
     </row>
     <row r="708">
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>90.77994537353516</v>
+        <v>90.77993774414062</v>
       </c>
     </row>
     <row r="709">
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>90.90558624267578</v>
+        <v>90.90556335449219</v>
       </c>
     </row>
     <row r="710">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="B710" t="n">
-        <v>91.332763671875</v>
+        <v>91.33274841308594</v>
       </c>
     </row>
     <row r="711">
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>91.62592315673828</v>
+        <v>91.62593078613281</v>
       </c>
     </row>
     <row r="712">
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B713" t="n">
-        <v>91.09822845458984</v>
+        <v>91.09824371337891</v>
       </c>
     </row>
     <row r="714">
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="B714" t="n">
-        <v>92.37139892578125</v>
+        <v>92.37139129638672</v>
       </c>
     </row>
     <row r="715">
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="B715" t="n">
-        <v>91.332763671875</v>
+        <v>91.33274841308594</v>
       </c>
     </row>
     <row r="716">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="B716" t="n">
-        <v>91.78506469726562</v>
+        <v>91.78507232666016</v>
       </c>
     </row>
     <row r="717">
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="B717" t="n">
-        <v>92.22061920166016</v>
+        <v>92.22062683105469</v>
       </c>
     </row>
     <row r="718">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="B720" t="n">
-        <v>92.12010192871094</v>
+        <v>92.1201171875</v>
       </c>
     </row>
     <row r="721">
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="B721" t="n">
-        <v>92.04472351074219</v>
+        <v>92.04473114013672</v>
       </c>
     </row>
     <row r="722">
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="B724" t="n">
-        <v>91.92745208740234</v>
+        <v>91.92745971679688</v>
       </c>
     </row>
     <row r="725">
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="B726" t="n">
-        <v>92.50540161132812</v>
+        <v>92.50541687011719</v>
       </c>
     </row>
     <row r="727">
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="B729" t="n">
-        <v>92.19548034667969</v>
+        <v>92.19549560546875</v>
       </c>
     </row>
     <row r="730">
@@ -7725,7 +7725,7 @@
         </is>
       </c>
       <c r="B731" t="n">
-        <v>91.19873809814453</v>
+        <v>91.19875335693359</v>
       </c>
     </row>
     <row r="732">
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="B732" t="n">
-        <v>91.93583679199219</v>
+        <v>91.93582916259766</v>
       </c>
     </row>
     <row r="733">
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="B733" t="n">
-        <v>93.04986572265625</v>
+        <v>93.04985809326172</v>
       </c>
     </row>
     <row r="734">
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="B734" t="n">
-        <v>90.46164703369141</v>
+        <v>90.46165466308594</v>
       </c>
     </row>
     <row r="735">
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="B735" t="n">
-        <v>91.13172912597656</v>
+        <v>91.13172149658203</v>
       </c>
     </row>
     <row r="736">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="B736" t="n">
-        <v>89.40627288818359</v>
+        <v>89.40626525878906</v>
       </c>
     </row>
     <row r="737">
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>87.93209075927734</v>
+        <v>87.93208312988281</v>
       </c>
     </row>
     <row r="738">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="B739" t="n">
-        <v>90.26899719238281</v>
+        <v>90.26898956298828</v>
       </c>
     </row>
     <row r="740">
@@ -7815,7 +7815,7 @@
         </is>
       </c>
       <c r="B740" t="n">
-        <v>91.85207366943359</v>
+        <v>91.85208129882812</v>
       </c>
     </row>
     <row r="741">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="B743" t="n">
-        <v>92.48867034912109</v>
+        <v>92.4886474609375</v>
       </c>
     </row>
     <row r="744">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="B745" t="n">
-        <v>93.64454650878906</v>
+        <v>93.64455413818359</v>
       </c>
     </row>
     <row r="746">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>92.44676971435547</v>
+        <v>92.44677734375</v>
       </c>
     </row>
     <row r="747">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="B747" t="n">
-        <v>93.74507141113281</v>
+        <v>93.74506378173828</v>
       </c>
     </row>
     <row r="748">
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="B748" t="n">
-        <v>93.7115478515625</v>
+        <v>93.71156311035156</v>
       </c>
     </row>
     <row r="749">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="B749" t="n">
-        <v>93.59429168701172</v>
+        <v>93.59429931640625</v>
       </c>
     </row>
     <row r="750">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B750" t="n">
-        <v>92.86557769775391</v>
+        <v>92.8656005859375</v>
       </c>
     </row>
     <row r="751">
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="B751" t="n">
-        <v>93.91259002685547</v>
+        <v>93.91258239746094</v>
       </c>
     </row>
     <row r="752">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="B752" t="n">
-        <v>94.8758544921875</v>
+        <v>94.87583160400391</v>
       </c>
     </row>
     <row r="753">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="B753" t="n">
-        <v>94.77532196044922</v>
+        <v>94.77532958984375</v>
       </c>
     </row>
     <row r="754">
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B755" t="n">
-        <v>96.73938751220703</v>
+        <v>96.7393798828125</v>
       </c>
     </row>
     <row r="756">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="B758" t="n">
-        <v>98.08367156982422</v>
+        <v>98.08367919921875</v>
       </c>
     </row>
     <row r="759">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="B759" t="n">
-        <v>97.31429290771484</v>
+        <v>97.31428527832031</v>
       </c>
     </row>
     <row r="760">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="B762" t="n">
-        <v>94.49884796142578</v>
+        <v>94.49886322021484</v>
       </c>
     </row>
     <row r="763">
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B763" t="n">
-        <v>93.87319183349609</v>
+        <v>93.87321472167969</v>
       </c>
     </row>
     <row r="764">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="B764" t="n">
-        <v>93.33210754394531</v>
+        <v>93.33209991455078</v>
       </c>
     </row>
     <row r="765">
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="B766" t="n">
-        <v>93.58574676513672</v>
+        <v>93.58575439453125</v>
       </c>
     </row>
     <row r="767">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>93.39974975585938</v>
+        <v>93.39973449707031</v>
       </c>
     </row>
     <row r="768">
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="B769" t="n">
-        <v>91.58196258544922</v>
+        <v>91.58195495605469</v>
       </c>
     </row>
     <row r="770">
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="B770" t="n">
-        <v>90.34757232666016</v>
+        <v>90.34757995605469</v>
       </c>
     </row>
     <row r="771">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="B771" t="n">
-        <v>89.18928527832031</v>
+        <v>89.18926239013672</v>
       </c>
     </row>
     <row r="772">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="B772" t="n">
-        <v>88.96944427490234</v>
+        <v>88.96945190429688</v>
       </c>
     </row>
     <row r="773">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="B773" t="n">
-        <v>89.13853454589844</v>
+        <v>89.13854217529297</v>
       </c>
     </row>
     <row r="774">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="B774" t="n">
-        <v>88.78343963623047</v>
+        <v>88.78343200683594</v>
       </c>
     </row>
     <row r="775">
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>85.95109558105469</v>
+        <v>85.95110321044922</v>
       </c>
     </row>
     <row r="777">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>89.50209045410156</v>
+        <v>89.50210571289062</v>
       </c>
     </row>
     <row r="780">
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="B781" t="n">
-        <v>89.67965698242188</v>
+        <v>89.67964172363281</v>
       </c>
     </row>
     <row r="782">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="B782" t="n">
-        <v>88.79191589355469</v>
+        <v>88.79189300537109</v>
       </c>
     </row>
     <row r="783">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="B784" t="n">
-        <v>88.25077056884766</v>
+        <v>88.25077819824219</v>
       </c>
     </row>
     <row r="785">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="B785" t="n">
-        <v>90.24611663818359</v>
+        <v>90.24610137939453</v>
       </c>
     </row>
     <row r="786">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="B786" t="n">
-        <v>88.11550140380859</v>
+        <v>88.11551666259766</v>
       </c>
     </row>
     <row r="787">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="B787" t="n">
-        <v>87.31231689453125</v>
+        <v>87.31232452392578</v>
       </c>
     </row>
     <row r="788">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>86.517578125</v>
+        <v>86.51756286621094</v>
       </c>
     </row>
     <row r="789">
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="B790" t="n">
-        <v>87.70124053955078</v>
+        <v>87.70123291015625</v>
       </c>
     </row>
     <row r="791">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="B792" t="n">
-        <v>86.24702453613281</v>
+        <v>86.24700927734375</v>
       </c>
     </row>
     <row r="793">
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="B793" t="n">
-        <v>85.93418121337891</v>
+        <v>85.9342041015625</v>
       </c>
     </row>
     <row r="794">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="B795" t="n">
-        <v>85.93418121337891</v>
+        <v>85.9342041015625</v>
       </c>
     </row>
     <row r="796">
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="B796" t="n">
-        <v>88.00559234619141</v>
+        <v>88.00560760498047</v>
       </c>
     </row>
     <row r="797">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>86.69510650634766</v>
+        <v>86.69511413574219</v>
       </c>
     </row>
     <row r="798">
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="B799" t="n">
-        <v>87.85340881347656</v>
+        <v>87.85342407226562</v>
       </c>
     </row>
     <row r="800">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="B803" t="n">
-        <v>86.79659271240234</v>
+        <v>86.79658508300781</v>
       </c>
     </row>
     <row r="804">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="B804" t="n">
-        <v>88.13242340087891</v>
+        <v>88.13243865966797</v>
       </c>
     </row>
     <row r="805">
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="B805" t="n">
-        <v>88.35226440429688</v>
+        <v>88.35225677490234</v>
       </c>
     </row>
     <row r="806">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="B807" t="n">
-        <v>86.96566009521484</v>
+        <v>86.96567535400391</v>
       </c>
     </row>
     <row r="808">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="B808" t="n">
-        <v>87.54904937744141</v>
+        <v>87.54903411865234</v>
       </c>
     </row>
     <row r="809">
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>88.58896636962891</v>
+        <v>88.58898162841797</v>
       </c>
     </row>
     <row r="810">
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="B810" t="n">
-        <v>89.95864868164062</v>
+        <v>89.95866394042969</v>
       </c>
     </row>
     <row r="811">
@@ -8525,7 +8525,7 @@
         </is>
       </c>
       <c r="B811" t="n">
-        <v>89.95864868164062</v>
+        <v>89.95866394042969</v>
       </c>
     </row>
     <row r="812">
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="B813" t="n">
-        <v>89.63735961914062</v>
+        <v>89.63737487792969</v>
       </c>
     </row>
     <row r="814">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="B814" t="n">
-        <v>88.63170623779297</v>
+        <v>88.63172149658203</v>
       </c>
     </row>
     <row r="815">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="B816" t="n">
-        <v>90.30640411376953</v>
+        <v>90.30641174316406</v>
       </c>
     </row>
     <row r="817">
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="B817" t="n">
-        <v>91.26702117919922</v>
+        <v>91.26702880859375</v>
       </c>
     </row>
     <row r="818">
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B818" t="n">
-        <v>93.94484710693359</v>
+        <v>93.94483947753906</v>
       </c>
     </row>
     <row r="819">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="B819" t="n">
-        <v>93.26475524902344</v>
+        <v>93.26476287841797</v>
       </c>
     </row>
     <row r="820">
@@ -8615,7 +8615,7 @@
         </is>
       </c>
       <c r="B820" t="n">
-        <v>92.12563323974609</v>
+        <v>92.12562561035156</v>
       </c>
     </row>
     <row r="821">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>93.91934967041016</v>
+        <v>93.91934204101562</v>
       </c>
     </row>
     <row r="822">
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="B822" t="n">
-        <v>93.46027374267578</v>
+        <v>93.46028900146484</v>
       </c>
     </row>
     <row r="823">
@@ -8645,7 +8645,7 @@
         </is>
       </c>
       <c r="B823" t="n">
-        <v>93.00123596191406</v>
+        <v>93.00121307373047</v>
       </c>
     </row>
     <row r="824">
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>94.10636138916016</v>
+        <v>94.10637664794922</v>
       </c>
     </row>
     <row r="825">
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="B825" t="n">
-        <v>93.17124938964844</v>
+        <v>93.17125701904297</v>
       </c>
     </row>
     <row r="826">
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="B826" t="n">
-        <v>93.32425689697266</v>
+        <v>93.32426452636719</v>
       </c>
     </row>
     <row r="827">
@@ -8685,7 +8685,7 @@
         </is>
       </c>
       <c r="B827" t="n">
-        <v>92.32114410400391</v>
+        <v>92.32115173339844</v>
       </c>
     </row>
     <row r="828">
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="B829" t="n">
-        <v>92.83969116210938</v>
+        <v>92.83971405029297</v>
       </c>
     </row>
     <row r="830">
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="B830" t="n">
-        <v>92.44016265869141</v>
+        <v>92.44017028808594</v>
       </c>
     </row>
     <row r="831">
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="B833" t="n">
-        <v>95.63655853271484</v>
+        <v>95.63653564453125</v>
       </c>
     </row>
     <row r="834">
@@ -8755,7 +8755,7 @@
         </is>
       </c>
       <c r="B834" t="n">
-        <v>94.97345733642578</v>
+        <v>94.97348022460938</v>
       </c>
     </row>
     <row r="835">
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="B836" t="n">
-        <v>93.06925201416016</v>
+        <v>93.06923675537109</v>
       </c>
     </row>
     <row r="837">
@@ -8805,7 +8805,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>92.61018371582031</v>
+        <v>92.61016845703125</v>
       </c>
     </row>
     <row r="840">
@@ -8815,7 +8815,7 @@
         </is>
       </c>
       <c r="B840" t="n">
-        <v>88.35964965820312</v>
+        <v>88.35968017578125</v>
       </c>
     </row>
     <row r="841">
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="B841" t="n">
-        <v>86.22592163085938</v>
+        <v>86.22591400146484</v>
       </c>
     </row>
     <row r="842">
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="B843" t="n">
-        <v>88.30014801025391</v>
+        <v>88.3001708984375</v>
       </c>
     </row>
     <row r="844">
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="B844" t="n">
-        <v>85.94537353515625</v>
+        <v>85.94539642333984</v>
       </c>
     </row>
     <row r="845">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="B846" t="n">
-        <v>81.18479156494141</v>
+        <v>81.184814453125</v>
       </c>
     </row>
     <row r="847">
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="B847" t="n">
-        <v>79.70561218261719</v>
+        <v>79.70562744140625</v>
       </c>
     </row>
     <row r="848">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>79.53561401367188</v>
+        <v>79.53559112548828</v>
       </c>
     </row>
     <row r="849">
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="B849" t="n">
-        <v>80.15618896484375</v>
+        <v>80.15617370605469</v>
       </c>
     </row>
     <row r="850">
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="B850" t="n">
-        <v>82.27291870117188</v>
+        <v>82.27292633056641</v>
       </c>
     </row>
     <row r="851">
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="B851" t="n">
-        <v>81.75435638427734</v>
+        <v>81.75437164306641</v>
       </c>
     </row>
     <row r="852">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="B852" t="n">
-        <v>82.86801147460938</v>
+        <v>82.86801910400391</v>
       </c>
     </row>
     <row r="853">
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="B853" t="n">
-        <v>80.46221160888672</v>
+        <v>80.46221923828125</v>
       </c>
     </row>
     <row r="854">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>80.10517883300781</v>
+        <v>80.10518646240234</v>
       </c>
     </row>
     <row r="855">
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="B855" t="n">
-        <v>80.615234375</v>
+        <v>80.61522674560547</v>
       </c>
     </row>
     <row r="856">
@@ -8975,7 +8975,7 @@
         </is>
       </c>
       <c r="B856" t="n">
-        <v>81.55035400390625</v>
+        <v>81.55034637451172</v>
       </c>
     </row>
     <row r="857">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>82.23891448974609</v>
+        <v>82.23890686035156</v>
       </c>
     </row>
     <row r="858">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="B858" t="n">
-        <v>82.93601989746094</v>
+        <v>82.93600463867188</v>
       </c>
     </row>
     <row r="859">
@@ -9005,7 +9005,7 @@
         </is>
       </c>
       <c r="B859" t="n">
-        <v>83.03804016113281</v>
+        <v>83.03803253173828</v>
       </c>
     </row>
     <row r="860">
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B860" t="n">
-        <v>85.26531219482422</v>
+        <v>85.26530456542969</v>
       </c>
     </row>
     <row r="861">
@@ -9025,7 +9025,7 @@
         </is>
       </c>
       <c r="B861" t="n">
-        <v>84.21968078613281</v>
+        <v>84.21965789794922</v>
       </c>
     </row>
     <row r="862">
@@ -9035,7 +9035,7 @@
         </is>
       </c>
       <c r="B862" t="n">
-        <v>83.52257537841797</v>
+        <v>83.5225830078125</v>
       </c>
     </row>
     <row r="863">
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="B863" t="n">
-        <v>84.67020416259766</v>
+        <v>84.67023468017578</v>
       </c>
     </row>
     <row r="864">
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="B865" t="n">
-        <v>83.27606201171875</v>
+        <v>83.27604675292969</v>
       </c>
     </row>
     <row r="866">
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="B867" t="n">
-        <v>82.47695159912109</v>
+        <v>82.47696685791016</v>
       </c>
     </row>
     <row r="868">
@@ -9095,7 +9095,7 @@
         </is>
       </c>
       <c r="B868" t="n">
-        <v>80.52173614501953</v>
+        <v>80.52172088623047</v>
       </c>
     </row>
     <row r="869">
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="B870" t="n">
-        <v>74.80052185058594</v>
+        <v>74.80052947998047</v>
       </c>
     </row>
     <row r="871">
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="B873" t="n">
-        <v>73.992919921875</v>
+        <v>73.99292755126953</v>
       </c>
     </row>
     <row r="874">
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="B874" t="n">
-        <v>74.55400085449219</v>
+        <v>74.55400848388672</v>
       </c>
     </row>
     <row r="875">
@@ -9165,7 +9165,7 @@
         </is>
       </c>
       <c r="B875" t="n">
-        <v>75.59111785888672</v>
+        <v>75.59112548828125</v>
       </c>
     </row>
     <row r="876">
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="B877" t="n">
-        <v>78.00612640380859</v>
+        <v>78.00611877441406</v>
       </c>
     </row>
     <row r="878">
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="B879" t="n">
-        <v>79.54607391357422</v>
+        <v>79.54606628417969</v>
       </c>
     </row>
     <row r="880">
@@ -9215,7 +9215,7 @@
         </is>
       </c>
       <c r="B880" t="n">
-        <v>78.57931518554688</v>
+        <v>78.57932281494141</v>
       </c>
     </row>
     <row r="881">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="B882" t="n">
-        <v>77.94625091552734</v>
+        <v>77.94624328613281</v>
       </c>
     </row>
     <row r="883">
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="B883" t="n">
-        <v>79.34928894042969</v>
+        <v>79.34929656982422</v>
       </c>
     </row>
     <row r="884">
@@ -9255,7 +9255,7 @@
         </is>
       </c>
       <c r="B884" t="n">
-        <v>79.12684631347656</v>
+        <v>79.12686157226562</v>
       </c>
     </row>
     <row r="885">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="B885" t="n">
-        <v>78.98141479492188</v>
+        <v>78.98140716552734</v>
       </c>
     </row>
     <row r="886">
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="B887" t="n">
-        <v>78.77609252929688</v>
+        <v>78.77608489990234</v>
       </c>
     </row>
     <row r="888">
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="B888" t="n">
-        <v>78.60498046875</v>
+        <v>78.60497283935547</v>
       </c>
     </row>
     <row r="889">
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="B889" t="n">
-        <v>78.29698944091797</v>
+        <v>78.2969970703125</v>
       </c>
     </row>
     <row r="890">
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="B890" t="n">
-        <v>77.92057037353516</v>
+        <v>77.92057800292969</v>
       </c>
     </row>
     <row r="891">
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="B894" t="n">
-        <v>79.99091339111328</v>
+        <v>79.99093627929688</v>
       </c>
     </row>
     <row r="895">
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="B895" t="n">
-        <v>79.80271911621094</v>
+        <v>79.80270385742188</v>
       </c>
     </row>
     <row r="896">
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="B896" t="n">
-        <v>80.43579864501953</v>
+        <v>80.435791015625</v>
       </c>
     </row>
     <row r="897">
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="B899" t="n">
-        <v>81.07741546630859</v>
+        <v>81.07743072509766</v>
       </c>
     </row>
     <row r="900">
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="B900" t="n">
-        <v>81.56507110595703</v>
+        <v>81.56508636474609</v>
       </c>
     </row>
     <row r="901">
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="B901" t="n">
-        <v>84.20862579345703</v>
+        <v>84.20863342285156</v>
       </c>
     </row>
     <row r="902">
@@ -9445,7 +9445,7 @@
         </is>
       </c>
       <c r="B903" t="n">
-        <v>83.97764587402344</v>
+        <v>83.97763824462891</v>
       </c>
     </row>
     <row r="904">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="B906" t="n">
-        <v>83.03656768798828</v>
+        <v>83.03656005859375</v>
       </c>
     </row>
     <row r="907">
@@ -9485,7 +9485,7 @@
         </is>
       </c>
       <c r="B907" t="n">
-        <v>83.26755523681641</v>
+        <v>83.26756286621094</v>
       </c>
     </row>
     <row r="908">
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="B908" t="n">
-        <v>84.01186370849609</v>
+        <v>84.01185607910156</v>
       </c>
     </row>
     <row r="909">
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="B909" t="n">
-        <v>84.47384643554688</v>
+        <v>84.47383117675781</v>
       </c>
     </row>
     <row r="910">
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="B910" t="n">
-        <v>85.75711059570312</v>
+        <v>85.75710296630859</v>
       </c>
     </row>
     <row r="911">
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="B911" t="n">
-        <v>85.55181121826172</v>
+        <v>85.55180358886719</v>
       </c>
     </row>
     <row r="912">
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>87.02328491210938</v>
+        <v>87.02326965332031</v>
       </c>
     </row>
     <row r="913">
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="B913" t="n">
-        <v>87.37405395507812</v>
+        <v>87.37404632568359</v>
       </c>
     </row>
     <row r="914">
@@ -9575,7 +9575,7 @@
         </is>
       </c>
       <c r="B916" t="n">
-        <v>86.04800415039062</v>
+        <v>86.04798126220703</v>
       </c>
     </row>
     <row r="917">
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="B917" t="n">
-        <v>85.14112854003906</v>
+        <v>85.14114379882812</v>
       </c>
     </row>
     <row r="918">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="B918" t="n">
-        <v>83.28465270996094</v>
+        <v>83.28466033935547</v>
       </c>
     </row>
     <row r="919">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="B919" t="n">
-        <v>82.21526336669922</v>
+        <v>82.21528625488281</v>
       </c>
     </row>
     <row r="920">
@@ -9625,7 +9625,7 @@
         </is>
       </c>
       <c r="B921" t="n">
-        <v>83.91774749755859</v>
+        <v>83.91776275634766</v>
       </c>
     </row>
     <row r="922">
@@ -9635,7 +9635,7 @@
         </is>
       </c>
       <c r="B922" t="n">
-        <v>81.80464172363281</v>
+        <v>81.80463409423828</v>
       </c>
     </row>
     <row r="923">
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="B923" t="n">
-        <v>81.06888580322266</v>
+        <v>81.06886291503906</v>
       </c>
     </row>
     <row r="924">
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="B924" t="n">
-        <v>79.94815826416016</v>
+        <v>79.94814300537109</v>
       </c>
     </row>
     <row r="925">
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="B925" t="n">
-        <v>79.57170867919922</v>
+        <v>79.57173156738281</v>
       </c>
     </row>
     <row r="926">
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="B926" t="n">
-        <v>79.71714782714844</v>
+        <v>79.7171630859375</v>
       </c>
     </row>
     <row r="927">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="B927" t="n">
-        <v>78.60498046875</v>
+        <v>78.60497283935547</v>
       </c>
     </row>
     <row r="928">
@@ -9695,7 +9695,7 @@
         </is>
       </c>
       <c r="B928" t="n">
-        <v>79.3150634765625</v>
+        <v>79.31507110595703</v>
       </c>
     </row>
     <row r="929">
@@ -9705,7 +9705,7 @@
         </is>
       </c>
       <c r="B929" t="n">
-        <v>80.86356353759766</v>
+        <v>80.86355590820312</v>
       </c>
     </row>
     <row r="930">
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="B930" t="n">
-        <v>81.08599090576172</v>
+        <v>81.08598327636719</v>
       </c>
     </row>
     <row r="931">
@@ -9735,7 +9735,7 @@
         </is>
       </c>
       <c r="B932" t="n">
-        <v>82.76279449462891</v>
+        <v>82.76278686523438</v>
       </c>
     </row>
     <row r="933">
@@ -9745,7 +9745,7 @@
         </is>
       </c>
       <c r="B933" t="n">
-        <v>79.59738159179688</v>
+        <v>79.59738922119141</v>
       </c>
     </row>
     <row r="934">
@@ -9755,7 +9755,7 @@
         </is>
       </c>
       <c r="B934" t="n">
-        <v>78.69056701660156</v>
+        <v>78.6905517578125</v>
       </c>
     </row>
     <row r="935">
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="B936" t="n">
-        <v>77.24469757080078</v>
+        <v>77.24471282958984</v>
       </c>
     </row>
     <row r="937">
@@ -9795,7 +9795,7 @@
         </is>
       </c>
       <c r="B938" t="n">
-        <v>75.25991058349609</v>
+        <v>75.25991821289062</v>
       </c>
     </row>
     <row r="939">
@@ -9805,7 +9805,7 @@
         </is>
       </c>
       <c r="B939" t="n">
-        <v>74.07074737548828</v>
+        <v>74.07073974609375</v>
       </c>
     </row>
     <row r="940">
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="B940" t="n">
-        <v>73.12968444824219</v>
+        <v>73.12969207763672</v>
       </c>
     </row>
     <row r="941">
@@ -9855,7 +9855,7 @@
         </is>
       </c>
       <c r="B944" t="n">
-        <v>70.63563537597656</v>
+        <v>70.63562774658203</v>
       </c>
     </row>
     <row r="945">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="B945" t="n">
-        <v>68.56014251708984</v>
+        <v>68.56015014648438</v>
       </c>
     </row>
     <row r="946">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="B946" t="n">
-        <v>69.32981109619141</v>
+        <v>69.32979583740234</v>
       </c>
     </row>
     <row r="947">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="B947" t="n">
-        <v>70.56645965576172</v>
+        <v>70.56643676757812</v>
       </c>
     </row>
     <row r="948">
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="B948" t="n">
-        <v>71.99333953857422</v>
+        <v>71.99334716796875</v>
       </c>
     </row>
     <row r="949">
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="B949" t="n">
-        <v>70.58376312255859</v>
+        <v>70.58375549316406</v>
       </c>
     </row>
     <row r="950">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="B951" t="n">
-        <v>66.96895599365234</v>
+        <v>66.96896362304688</v>
       </c>
     </row>
     <row r="952">
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="B953" t="n">
-        <v>67.01218414306641</v>
+        <v>67.01217651367188</v>
       </c>
     </row>
     <row r="954">
@@ -9955,7 +9955,7 @@
         </is>
       </c>
       <c r="B954" t="n">
-        <v>66.31170654296875</v>
+        <v>66.31171417236328</v>
       </c>
     </row>
     <row r="955">
@@ -9965,7 +9965,7 @@
         </is>
       </c>
       <c r="B955" t="n">
-        <v>67.52242279052734</v>
+        <v>67.52240753173828</v>
       </c>
     </row>
     <row r="956">
@@ -9975,7 +9975,7 @@
         </is>
       </c>
       <c r="B956" t="n">
-        <v>65.8447265625</v>
+        <v>65.84473419189453</v>
       </c>
     </row>
     <row r="957">
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B957" t="n">
-        <v>68.32665252685547</v>
+        <v>68.32666015625</v>
       </c>
     </row>
     <row r="958">
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="B958" t="n">
-        <v>69.07036590576172</v>
+        <v>69.07038879394531</v>
       </c>
     </row>
     <row r="959">
@@ -10015,7 +10015,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>67.055419921875</v>
+        <v>67.05542755126953</v>
       </c>
     </row>
     <row r="961">
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="B961" t="n">
-        <v>67.58293914794922</v>
+        <v>67.58295440673828</v>
       </c>
     </row>
     <row r="962">
@@ -10035,7 +10035,7 @@
         </is>
       </c>
       <c r="B962" t="n">
-        <v>67.57430267333984</v>
+        <v>67.57429504394531</v>
       </c>
     </row>
     <row r="963">
@@ -10045,7 +10045,7 @@
         </is>
       </c>
       <c r="B963" t="n">
-        <v>70.22918701171875</v>
+        <v>70.22917175292969</v>
       </c>
     </row>
     <row r="964">
@@ -10055,7 +10055,7 @@
         </is>
       </c>
       <c r="B964" t="n">
-        <v>70.18595123291016</v>
+        <v>70.18595886230469</v>
       </c>
     </row>
     <row r="965">
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="B965" t="n">
-        <v>70.28970336914062</v>
+        <v>70.28972625732422</v>
       </c>
     </row>
     <row r="966">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="B966" t="n">
-        <v>71.83767700195312</v>
+        <v>71.83769226074219</v>
       </c>
     </row>
     <row r="967">
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="B971" t="n">
-        <v>70.61834716796875</v>
+        <v>70.61833953857422</v>
       </c>
     </row>
     <row r="972">
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="B972" t="n">
-        <v>70.61834716796875</v>
+        <v>70.61833953857422</v>
       </c>
     </row>
     <row r="973">
@@ -10155,7 +10155,7 @@
         </is>
       </c>
       <c r="B974" t="n">
-        <v>70.10812377929688</v>
+        <v>70.10811614990234</v>
       </c>
     </row>
     <row r="975">
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="B975" t="n">
-        <v>75.23628997802734</v>
+        <v>75.23629760742188</v>
       </c>
     </row>
     <row r="976">
@@ -10175,7 +10175,7 @@
         </is>
       </c>
       <c r="B976" t="n">
-        <v>75.22764587402344</v>
+        <v>75.22763824462891</v>
       </c>
     </row>
     <row r="977">
@@ -10185,7 +10185,7 @@
         </is>
       </c>
       <c r="B977" t="n">
-        <v>73.39430999755859</v>
+        <v>73.39430236816406</v>
       </c>
     </row>
     <row r="978">
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="B978" t="n">
-        <v>74.18988800048828</v>
+        <v>74.18989562988281</v>
       </c>
     </row>
     <row r="979">
@@ -10225,7 +10225,7 @@
         </is>
       </c>
       <c r="B981" t="n">
-        <v>73.93911743164062</v>
+        <v>73.93910980224609</v>
       </c>
     </row>
     <row r="982">
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="B983" t="n">
-        <v>74.73471069335938</v>
+        <v>74.73472595214844</v>
       </c>
     </row>
     <row r="984">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="B984" t="n">
-        <v>74.79523468017578</v>
+        <v>74.79522705078125</v>
       </c>
     </row>
     <row r="985">
@@ -10265,7 +10265,7 @@
         </is>
       </c>
       <c r="B985" t="n">
-        <v>75.2708740234375</v>
+        <v>75.27088165283203</v>
       </c>
     </row>
     <row r="986">
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="B986" t="n">
-        <v>73.25594329833984</v>
+        <v>73.25592803955078</v>
       </c>
     </row>
     <row r="987">
@@ -10285,7 +10285,7 @@
         </is>
       </c>
       <c r="B987" t="n">
-        <v>74.46662139892578</v>
+        <v>74.46664428710938</v>
       </c>
     </row>
     <row r="988">
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="B988" t="n">
-        <v>76.17024993896484</v>
+        <v>76.17026519775391</v>
       </c>
     </row>
     <row r="989">
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="B990" t="n">
-        <v>75.78108978271484</v>
+        <v>75.78108215332031</v>
       </c>
     </row>
     <row r="991">
@@ -10325,7 +10325,7 @@
         </is>
       </c>
       <c r="B991" t="n">
-        <v>74.39743804931641</v>
+        <v>74.39744567871094</v>
       </c>
     </row>
     <row r="992">
@@ -10345,7 +10345,7 @@
         </is>
       </c>
       <c r="B993" t="n">
-        <v>73.843994140625</v>
+        <v>73.84398651123047</v>
       </c>
     </row>
     <row r="994">
@@ -10355,7 +10355,7 @@
         </is>
       </c>
       <c r="B994" t="n">
-        <v>74.36286163330078</v>
+        <v>74.36284637451172</v>
       </c>
     </row>
     <row r="995">
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="B996" t="n">
-        <v>74.79523468017578</v>
+        <v>74.79522705078125</v>
       </c>
     </row>
     <row r="997">
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="B998" t="n">
-        <v>75.6600341796875</v>
+        <v>75.66001892089844</v>
       </c>
     </row>
     <row r="999">
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="B1000" t="n">
-        <v>72.71975708007812</v>
+        <v>72.71977233886719</v>
       </c>
     </row>
     <row r="1001">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="B1004" t="n">
-        <v>71.92339324951172</v>
+        <v>71.92338562011719</v>
       </c>
     </row>
     <row r="1005">
@@ -10465,7 +10465,7 @@
         </is>
       </c>
       <c r="B1005" t="n">
-        <v>72.5635986328125</v>
+        <v>72.56360626220703</v>
       </c>
     </row>
     <row r="1006">
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="B1007" t="n">
-        <v>71.30070495605469</v>
+        <v>71.30072021484375</v>
       </c>
     </row>
     <row r="1008">
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="B1010" t="n">
-        <v>72.40573883056641</v>
+        <v>72.40575408935547</v>
       </c>
     </row>
     <row r="1011">
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="B1011" t="n">
-        <v>74.04575347900391</v>
+        <v>74.04574584960938</v>
       </c>
     </row>
     <row r="1012">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="B1015" t="n">
-        <v>74.18607330322266</v>
+        <v>74.18608093261719</v>
       </c>
     </row>
     <row r="1016">
@@ -10575,7 +10575,7 @@
         </is>
       </c>
       <c r="B1016" t="n">
-        <v>76.84341430664062</v>
+        <v>76.84340667724609</v>
       </c>
     </row>
     <row r="1017">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="B1017" t="n">
-        <v>77.81689453125</v>
+        <v>77.81687927246094</v>
       </c>
     </row>
     <row r="1018">
@@ -10595,7 +10595,7 @@
         </is>
       </c>
       <c r="B1018" t="n">
-        <v>77.33452606201172</v>
+        <v>77.33453369140625</v>
       </c>
     </row>
     <row r="1019">
@@ -10605,7 +10605,7 @@
         </is>
       </c>
       <c r="B1019" t="n">
-        <v>77.55377960205078</v>
+        <v>77.55380249023438</v>
       </c>
     </row>
     <row r="1020">
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="B1020" t="n">
-        <v>76.42243957519531</v>
+        <v>76.42242431640625</v>
       </c>
     </row>
     <row r="1021">
@@ -10625,7 +10625,7 @@
         </is>
       </c>
       <c r="B1021" t="n">
-        <v>76.00147247314453</v>
+        <v>76.00148010253906</v>
       </c>
     </row>
     <row r="1022">
@@ -10635,7 +10635,7 @@
         </is>
       </c>
       <c r="B1022" t="n">
-        <v>76.90479278564453</v>
+        <v>76.90480041503906</v>
       </c>
     </row>
     <row r="1023">
@@ -10645,7 +10645,7 @@
         </is>
       </c>
       <c r="B1023" t="n">
-        <v>77.25558471679688</v>
+        <v>77.25559234619141</v>
       </c>
     </row>
     <row r="1024">
@@ -10655,7 +10655,7 @@
         </is>
       </c>
       <c r="B1024" t="n">
-        <v>77.44852447509766</v>
+        <v>77.44853973388672</v>
       </c>
     </row>
     <row r="1025">
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="B1026" t="n">
-        <v>78.35184478759766</v>
+        <v>78.35186767578125</v>
       </c>
     </row>
     <row r="1027">
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="B1027" t="n">
-        <v>79.22885894775391</v>
+        <v>79.22887420654297</v>
       </c>
     </row>
     <row r="1028">
@@ -10705,7 +10705,7 @@
         </is>
       </c>
       <c r="B1029" t="n">
-        <v>79.86030578613281</v>
+        <v>79.86029815673828</v>
       </c>
     </row>
     <row r="1030">
@@ -10715,7 +10715,7 @@
         </is>
       </c>
       <c r="B1030" t="n">
-        <v>80.35142517089844</v>
+        <v>80.35143280029297</v>
       </c>
     </row>
     <row r="1031">
@@ -10755,7 +10755,7 @@
         </is>
       </c>
       <c r="B1034" t="n">
-        <v>79.86909484863281</v>
+        <v>79.86908721923828</v>
       </c>
     </row>
     <row r="1035">
@@ -10775,7 +10775,7 @@
         </is>
       </c>
       <c r="B1036" t="n">
-        <v>78.62373352050781</v>
+        <v>78.62371826171875</v>
       </c>
     </row>
     <row r="1037">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="B1038" t="n">
-        <v>79.59719848632812</v>
+        <v>79.59720611572266</v>
       </c>
     </row>
     <row r="1039">
@@ -10815,7 +10815,7 @@
         </is>
       </c>
       <c r="B1040" t="n">
-        <v>79.28147888183594</v>
+        <v>79.28148651123047</v>
       </c>
     </row>
     <row r="1041">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="B1041" t="n">
-        <v>78.50971221923828</v>
+        <v>78.50972747802734</v>
       </c>
     </row>
     <row r="1042">
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="B1043" t="n">
-        <v>76.63291168212891</v>
+        <v>76.63291931152344</v>
       </c>
     </row>
     <row r="1044">
@@ -10865,7 +10865,7 @@
         </is>
       </c>
       <c r="B1045" t="n">
-        <v>76.51013946533203</v>
+        <v>76.51014709472656</v>
       </c>
     </row>
     <row r="1046">
@@ -10875,7 +10875,7 @@
         </is>
       </c>
       <c r="B1046" t="n">
-        <v>75.16831970214844</v>
+        <v>75.16832733154297</v>
       </c>
     </row>
     <row r="1047">
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="B1047" t="n">
-        <v>75.28234100341797</v>
+        <v>75.28233337402344</v>
       </c>
     </row>
     <row r="1048">
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="B1048" t="n">
-        <v>75.17710113525391</v>
+        <v>75.17708587646484</v>
       </c>
     </row>
     <row r="1049">
@@ -10925,7 +10925,7 @@
         </is>
       </c>
       <c r="B1051" t="n">
-        <v>76.23826599121094</v>
+        <v>76.23828125</v>
       </c>
     </row>
     <row r="1052">
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="B1053" t="n">
-        <v>74.16854095458984</v>
+        <v>74.16853332519531</v>
       </c>
     </row>
     <row r="1054">
@@ -10955,7 +10955,7 @@
         </is>
       </c>
       <c r="B1054" t="n">
-        <v>75.01922607421875</v>
+        <v>75.01923370361328</v>
       </c>
     </row>
     <row r="1055">
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="B1055" t="n">
-        <v>73.30029296875</v>
+        <v>73.30028533935547</v>
       </c>
     </row>
     <row r="1056">
@@ -10975,7 +10975,7 @@
         </is>
       </c>
       <c r="B1056" t="n">
-        <v>70.87097930908203</v>
+        <v>70.87098693847656</v>
       </c>
     </row>
     <row r="1057">
@@ -10985,7 +10985,7 @@
         </is>
       </c>
       <c r="B1057" t="n">
-        <v>71.80061340332031</v>
+        <v>71.80062103271484</v>
       </c>
     </row>
     <row r="1058">
@@ -10995,7 +10995,7 @@
         </is>
       </c>
       <c r="B1058" t="n">
-        <v>72.49343872070312</v>
+        <v>72.49343109130859</v>
       </c>
     </row>
     <row r="1059">
@@ -11005,7 +11005,7 @@
         </is>
       </c>
       <c r="B1059" t="n">
-        <v>72.44081878662109</v>
+        <v>72.44082641601562</v>
       </c>
     </row>
     <row r="1060">
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="B1060" t="n">
-        <v>72.282958984375</v>
+        <v>72.28296661376953</v>
       </c>
     </row>
     <row r="1061">
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B1062" t="n">
-        <v>71.44980621337891</v>
+        <v>71.44979858398438</v>
       </c>
     </row>
     <row r="1063">
@@ -11055,7 +11055,7 @@
         </is>
       </c>
       <c r="B1064" t="n">
-        <v>68.47676849365234</v>
+        <v>68.47674560546875</v>
       </c>
     </row>
     <row r="1065">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="B1065" t="n">
-        <v>68.04701995849609</v>
+        <v>68.04702758789062</v>
       </c>
     </row>
     <row r="1066">
@@ -11095,7 +11095,7 @@
         </is>
       </c>
       <c r="B1068" t="n">
-        <v>69.54400634765625</v>
+        <v>69.54401397705078</v>
       </c>
     </row>
     <row r="1069">
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="B1069" t="n">
-        <v>71.08529663085938</v>
+        <v>71.08531188964844</v>
       </c>
     </row>
     <row r="1070">
@@ -11115,7 +11115,7 @@
         </is>
       </c>
       <c r="B1070" t="n">
-        <v>72.01538848876953</v>
+        <v>72.01539611816406</v>
       </c>
     </row>
     <row r="1071">
@@ -11125,7 +11125,7 @@
         </is>
       </c>
       <c r="B1071" t="n">
-        <v>73.55667114257812</v>
+        <v>73.55668640136719</v>
       </c>
     </row>
     <row r="1072">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B1072" t="n">
-        <v>72.97205352783203</v>
+        <v>72.9720458984375</v>
       </c>
     </row>
     <row r="1073">
@@ -11145,7 +11145,7 @@
         </is>
       </c>
       <c r="B1073" t="n">
-        <v>72.87461853027344</v>
+        <v>72.87461090087891</v>
       </c>
     </row>
     <row r="1074">
@@ -11155,7 +11155,7 @@
         </is>
       </c>
       <c r="B1074" t="n">
-        <v>72.48487854003906</v>
+        <v>72.48484802246094</v>
       </c>
     </row>
     <row r="1075">
@@ -11165,7 +11165,7 @@
         </is>
       </c>
       <c r="B1075" t="n">
-        <v>72.98091888427734</v>
+        <v>72.98091125488281</v>
       </c>
     </row>
     <row r="1076">
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="B1076" t="n">
-        <v>73.31751251220703</v>
+        <v>73.31752777099609</v>
       </c>
     </row>
     <row r="1077">
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="B1077" t="n">
-        <v>73.62754058837891</v>
+        <v>73.62754821777344</v>
       </c>
     </row>
     <row r="1078">
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="B1079" t="n">
-        <v>73.05177307128906</v>
+        <v>73.05176544189453</v>
       </c>
     </row>
     <row r="1080">
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="B1080" t="n">
-        <v>71.91796875</v>
+        <v>71.91794586181641</v>
       </c>
     </row>
     <row r="1081">
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="B1081" t="n">
-        <v>73.41493988037109</v>
+        <v>73.41494750976562</v>
       </c>
     </row>
     <row r="1082">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="B1083" t="n">
-        <v>73.68069458007812</v>
+        <v>73.68070220947266</v>
       </c>
     </row>
     <row r="1084">
@@ -11265,7 +11265,7 @@
         </is>
       </c>
       <c r="B1085" t="n">
-        <v>72.96319580078125</v>
+        <v>72.96318817138672</v>
       </c>
     </row>
     <row r="1086">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="B1086" t="n">
-        <v>72.68858337402344</v>
+        <v>72.68859100341797</v>
       </c>
     </row>
     <row r="1087">
@@ -11285,7 +11285,7 @@
         </is>
       </c>
       <c r="B1087" t="n">
-        <v>71.97109222412109</v>
+        <v>71.97110748291016</v>
       </c>
     </row>
     <row r="1088">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="B1089" t="n">
-        <v>72.89232635498047</v>
+        <v>72.89231872558594</v>
       </c>
     </row>
     <row r="1090">
@@ -11335,7 +11335,7 @@
         </is>
       </c>
       <c r="B1092" t="n">
-        <v>71.99765777587891</v>
+        <v>71.99767303466797</v>
       </c>
     </row>
     <row r="1093">
@@ -11345,7 +11345,7 @@
         </is>
       </c>
       <c r="B1093" t="n">
-        <v>71.71422576904297</v>
+        <v>71.71421813964844</v>
       </c>
     </row>
     <row r="1094">
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="B1095" t="n">
-        <v>73.51238250732422</v>
+        <v>73.51237487792969</v>
       </c>
     </row>
     <row r="1096">
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="B1099" t="n">
-        <v>72.67088317871094</v>
+        <v>72.67087554931641</v>
       </c>
     </row>
     <row r="1100">
@@ -11415,7 +11415,7 @@
         </is>
       </c>
       <c r="B1100" t="n">
-        <v>72.66202545166016</v>
+        <v>72.66201782226562</v>
       </c>
     </row>
     <row r="1101">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="B1102" t="n">
-        <v>70.72212982177734</v>
+        <v>70.72211456298828</v>
       </c>
     </row>
     <row r="1103">
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="B1103" t="n">
-        <v>71.67877960205078</v>
+        <v>71.67878723144531</v>
       </c>
     </row>
     <row r="1104">
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="B1104" t="n">
-        <v>71.33332824707031</v>
+        <v>71.33332061767578</v>
       </c>
     </row>
     <row r="1105">
@@ -11475,7 +11475,7 @@
         </is>
       </c>
       <c r="B1106" t="n">
-        <v>71.65220642089844</v>
+        <v>71.6522216796875</v>
       </c>
     </row>
     <row r="1107">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="B1107" t="n">
-        <v>70.97899627685547</v>
+        <v>70.97901153564453</v>
       </c>
     </row>
     <row r="1108">
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="B1108" t="n">
-        <v>69.45545959472656</v>
+        <v>69.4554443359375</v>
       </c>
     </row>
     <row r="1109">
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="B1109" t="n">
-        <v>69.44656372070312</v>
+        <v>69.44657897949219</v>
       </c>
     </row>
     <row r="1110">
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="B1110" t="n">
-        <v>70.24378204345703</v>
+        <v>70.24379730224609</v>
       </c>
     </row>
     <row r="1111">
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="B1111" t="n">
-        <v>70.50953674316406</v>
+        <v>70.50952911376953</v>
       </c>
     </row>
     <row r="1112">
@@ -11535,7 +11535,7 @@
         </is>
       </c>
       <c r="B1112" t="n">
-        <v>70.86385345458984</v>
+        <v>70.86386108398438</v>
       </c>
     </row>
     <row r="1113">
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="B1113" t="n">
-        <v>70.87271881103516</v>
+        <v>70.87271118164062</v>
       </c>
     </row>
     <row r="1114">
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B1114" t="n">
-        <v>72.60002136230469</v>
+        <v>72.60001373291016</v>
       </c>
     </row>
     <row r="1115">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="B1115" t="n">
-        <v>72.09510803222656</v>
+        <v>72.09512329101562</v>
       </c>
     </row>
     <row r="1116">
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="B1116" t="n">
-        <v>72.78603363037109</v>
+        <v>72.78602600097656</v>
       </c>
     </row>
     <row r="1117">
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="B1117" t="n">
-        <v>74.12358856201172</v>
+        <v>74.12358093261719</v>
       </c>
     </row>
     <row r="1118">
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="B1118" t="n">
-        <v>73.66298675537109</v>
+        <v>73.66297912597656</v>
       </c>
     </row>
     <row r="1119">
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="B1121" t="n">
-        <v>73.7249755859375</v>
+        <v>73.72498321533203</v>
       </c>
     </row>
     <row r="1122">
@@ -11635,7 +11635,7 @@
         </is>
       </c>
       <c r="B1122" t="n">
-        <v>73.99958801269531</v>
+        <v>73.99958038330078</v>
       </c>
     </row>
     <row r="1123">
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="B1123" t="n">
-        <v>74.38935089111328</v>
+        <v>74.38933563232422</v>
       </c>
     </row>
     <row r="1124">
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="B1124" t="n">
-        <v>74.336181640625</v>
+        <v>74.33616638183594</v>
       </c>
     </row>
     <row r="1125">
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="B1125" t="n">
-        <v>73.45925140380859</v>
+        <v>73.45924377441406</v>
       </c>
     </row>
     <row r="1126">
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="B1127" t="n">
-        <v>71.97109222412109</v>
+        <v>71.97110748291016</v>
       </c>
     </row>
     <row r="1128">
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="B1128" t="n">
-        <v>70.97899627685547</v>
+        <v>70.97901153564453</v>
       </c>
     </row>
     <row r="1129">
@@ -11705,7 +11705,7 @@
         </is>
       </c>
       <c r="B1129" t="n">
-        <v>72.61774444580078</v>
+        <v>72.61772918701172</v>
       </c>
     </row>
     <row r="1130">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="B1130" t="n">
-        <v>73.51238250732422</v>
+        <v>73.51237487792969</v>
       </c>
     </row>
     <row r="1131">
@@ -11745,7 +11745,7 @@
         </is>
       </c>
       <c r="B1133" t="n">
-        <v>74.85308837890625</v>
+        <v>74.85310363769531</v>
       </c>
     </row>
     <row r="1134">
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="B1134" t="n">
-        <v>75.587646484375</v>
+        <v>75.58765411376953</v>
       </c>
     </row>
     <row r="1135">
@@ -11775,7 +11775,7 @@
         </is>
       </c>
       <c r="B1136" t="n">
-        <v>75.17558288574219</v>
+        <v>75.17559051513672</v>
       </c>
     </row>
     <row r="1137">
@@ -11795,7 +11795,7 @@
         </is>
       </c>
       <c r="B1138" t="n">
-        <v>75.32787322998047</v>
+        <v>75.327880859375</v>
       </c>
     </row>
     <row r="1139">
@@ -11805,7 +11805,7 @@
         </is>
       </c>
       <c r="B1139" t="n">
-        <v>76.40283203125</v>
+        <v>76.40283966064453</v>
       </c>
     </row>
     <row r="1140">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="B1141" t="n">
-        <v>77.30758666992188</v>
+        <v>77.30759429931641</v>
       </c>
     </row>
     <row r="1142">
@@ -11835,7 +11835,7 @@
         </is>
       </c>
       <c r="B1142" t="n">
-        <v>77.15531158447266</v>
+        <v>77.15528869628906</v>
       </c>
     </row>
     <row r="1143">
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="B1143" t="n">
-        <v>76.65365600585938</v>
+        <v>76.65364837646484</v>
       </c>
     </row>
     <row r="1144">
@@ -11855,7 +11855,7 @@
         </is>
       </c>
       <c r="B1144" t="n">
-        <v>76.23262786865234</v>
+        <v>76.23263549804688</v>
       </c>
     </row>
     <row r="1145">
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="B1145" t="n">
-        <v>77.09259033203125</v>
+        <v>77.09259796142578</v>
       </c>
     </row>
     <row r="1146">
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="B1146" t="n">
-        <v>76.84177398681641</v>
+        <v>76.84178161621094</v>
       </c>
     </row>
     <row r="1147">
@@ -11885,7 +11885,7 @@
         </is>
       </c>
       <c r="B1147" t="n">
-        <v>77.20011138916016</v>
+        <v>77.20009613037109</v>
       </c>
     </row>
     <row r="1148">
@@ -11895,7 +11895,7 @@
         </is>
       </c>
       <c r="B1148" t="n">
-        <v>77.83612060546875</v>
+        <v>77.83611297607422</v>
       </c>
     </row>
     <row r="1149">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="B1149" t="n">
-        <v>77.28072357177734</v>
+        <v>77.28070831298828</v>
       </c>
     </row>
     <row r="1150">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="B1150" t="n">
-        <v>77.63009643554688</v>
+        <v>77.63008117675781</v>
       </c>
     </row>
     <row r="1151">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="B1151" t="n">
-        <v>75.94596862792969</v>
+        <v>75.94597625732422</v>
       </c>
     </row>
     <row r="1152">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="B1152" t="n">
-        <v>75.88325500488281</v>
+        <v>75.88327789306641</v>
       </c>
     </row>
     <row r="1153">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="B1153" t="n">
-        <v>76.37596893310547</v>
+        <v>76.37596130371094</v>
       </c>
     </row>
     <row r="1154">
@@ -11955,7 +11955,7 @@
         </is>
       </c>
       <c r="B1154" t="n">
-        <v>76.25054931640625</v>
+        <v>76.25055694580078</v>
       </c>
     </row>
     <row r="1155">
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="B1155" t="n">
-        <v>75.81159210205078</v>
+        <v>75.81159973144531</v>
       </c>
     </row>
     <row r="1156">
@@ -11975,7 +11975,7 @@
         </is>
       </c>
       <c r="B1156" t="n">
-        <v>74.98745727539062</v>
+        <v>74.98747253417969</v>
       </c>
     </row>
     <row r="1157">
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="B1157" t="n">
-        <v>74.37831115722656</v>
+        <v>74.37832641601562</v>
       </c>
     </row>
     <row r="1158">
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="B1158" t="n">
-        <v>75.30995941162109</v>
+        <v>75.30996704101562</v>
       </c>
     </row>
     <row r="1159">
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="B1161" t="n">
-        <v>74.53060913085938</v>
+        <v>74.53059387207031</v>
       </c>
     </row>
     <row r="1162">
@@ -12035,7 +12035,7 @@
         </is>
       </c>
       <c r="B1162" t="n">
-        <v>74.64707183837891</v>
+        <v>74.64705657958984</v>
       </c>
     </row>
     <row r="1163">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="B1163" t="n">
-        <v>74.15438079833984</v>
+        <v>74.15437316894531</v>
       </c>
     </row>
     <row r="1164">
@@ -12055,7 +12055,7 @@
         </is>
       </c>
       <c r="B1164" t="n">
-        <v>73.32127380371094</v>
+        <v>73.32128143310547</v>
       </c>
     </row>
     <row r="1165">
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="B1167" t="n">
-        <v>72.05819702148438</v>
+        <v>72.05820465087891</v>
       </c>
     </row>
     <row r="1168">
@@ -12095,7 +12095,7 @@
         </is>
       </c>
       <c r="B1168" t="n">
-        <v>71.39530181884766</v>
+        <v>71.39529418945312</v>
       </c>
     </row>
     <row r="1169">
@@ -12105,7 +12105,7 @@
         </is>
       </c>
       <c r="B1169" t="n">
-        <v>71.60134887695312</v>
+        <v>71.60134124755859</v>
       </c>
     </row>
     <row r="1170">
@@ -12125,7 +12125,7 @@
         </is>
       </c>
       <c r="B1171" t="n">
-        <v>72.45235443115234</v>
+        <v>72.45233917236328</v>
       </c>
     </row>
     <row r="1172">
@@ -12145,7 +12145,7 @@
         </is>
       </c>
       <c r="B1173" t="n">
-        <v>73.18689727783203</v>
+        <v>73.18690490722656</v>
       </c>
     </row>
     <row r="1174">
@@ -12165,7 +12165,7 @@
         </is>
       </c>
       <c r="B1175" t="n">
-        <v>74.34249877929688</v>
+        <v>74.34248352050781</v>
       </c>
     </row>
     <row r="1176">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="B1176" t="n">
-        <v>73.79603576660156</v>
+        <v>73.79605102539062</v>
       </c>
     </row>
     <row r="1177">
@@ -12215,7 +12215,7 @@
         </is>
       </c>
       <c r="B1180" t="n">
-        <v>73.36607360839844</v>
+        <v>73.36608123779297</v>
       </c>
     </row>
     <row r="1181">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="B1182" t="n">
-        <v>73.08837890625</v>
+        <v>73.08836364746094</v>
       </c>
     </row>
     <row r="1183">
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="B1183" t="n">
-        <v>73.05255126953125</v>
+        <v>73.05253601074219</v>
       </c>
     </row>
     <row r="1184">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="B1185" t="n">
-        <v>73.56314849853516</v>
+        <v>73.56315612792969</v>
       </c>
     </row>
     <row r="1186">
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="B1189" t="n">
-        <v>72.36277008056641</v>
+        <v>72.36277770996094</v>
       </c>
     </row>
     <row r="1190">
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="B1190" t="n">
-        <v>69.89932250976562</v>
+        <v>69.89931488037109</v>
       </c>
     </row>
     <row r="1191">
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="B1191" t="n">
-        <v>69.37079620361328</v>
+        <v>69.37081146240234</v>
       </c>
     </row>
     <row r="1192">
@@ -12345,7 +12345,7 @@
         </is>
       </c>
       <c r="B1193" t="n">
-        <v>68.04502105712891</v>
+        <v>68.04501342773438</v>
       </c>
     </row>
     <row r="1194">
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="B1194" t="n">
-        <v>67.58815002441406</v>
+        <v>67.58815765380859</v>
       </c>
     </row>
     <row r="1195">
@@ -12365,7 +12365,7 @@
         </is>
       </c>
       <c r="B1195" t="n">
-        <v>68.2366943359375</v>
+        <v>68.23670196533203</v>
       </c>
     </row>
     <row r="1196">
@@ -12375,7 +12375,7 @@
         </is>
       </c>
       <c r="B1196" t="n">
-        <v>68.43569183349609</v>
+        <v>68.43568420410156</v>
       </c>
     </row>
     <row r="1197">
@@ -12395,7 +12395,7 @@
         </is>
       </c>
       <c r="B1198" t="n">
-        <v>65.86686706542969</v>
+        <v>65.86685943603516</v>
       </c>
     </row>
     <row r="1199">
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="B1199" t="n">
-        <v>66.67189025878906</v>
+        <v>66.67188262939453</v>
       </c>
     </row>
     <row r="1200">
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="B1200" t="n">
-        <v>67.04273986816406</v>
+        <v>67.04273223876953</v>
       </c>
     </row>
     <row r="1201">
@@ -12435,7 +12435,7 @@
         </is>
       </c>
       <c r="B1202" t="n">
-        <v>67.95628356933594</v>
+        <v>67.956298828125</v>
       </c>
     </row>
     <row r="1203">
@@ -12445,7 +12445,7 @@
         </is>
       </c>
       <c r="B1203" t="n">
-        <v>68.28191375732422</v>
+        <v>68.28192138671875</v>
       </c>
     </row>
     <row r="1204">
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="B1205" t="n">
-        <v>68.45378112792969</v>
+        <v>68.45378875732422</v>
       </c>
     </row>
     <row r="1206">
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="B1206" t="n">
-        <v>68.28191375732422</v>
+        <v>68.28192138671875</v>
       </c>
     </row>
     <row r="1207">
@@ -12485,7 +12485,7 @@
         </is>
       </c>
       <c r="B1207" t="n">
-        <v>69.09597778320312</v>
+        <v>69.09599304199219</v>
       </c>
     </row>
     <row r="1208">
@@ -12495,7 +12495,7 @@
         </is>
       </c>
       <c r="B1208" t="n">
-        <v>68.99649047851562</v>
+        <v>68.99649810791016</v>
       </c>
     </row>
     <row r="1209">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="B1209" t="n">
-        <v>67.53118133544922</v>
+        <v>67.53116607666016</v>
       </c>
     </row>
     <row r="1210">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="B1211" t="n">
-        <v>65.48696136474609</v>
+        <v>65.48697662353516</v>
       </c>
     </row>
     <row r="1212">
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="B1213" t="n">
-        <v>65.67691802978516</v>
+        <v>65.67690277099609</v>
       </c>
     </row>
     <row r="1214">
@@ -12565,7 +12565,7 @@
         </is>
       </c>
       <c r="B1215" t="n">
-        <v>65.49602508544922</v>
+        <v>65.49601745605469</v>
       </c>
     </row>
     <row r="1216">
@@ -12575,7 +12575,7 @@
         </is>
       </c>
       <c r="B1216" t="n">
-        <v>64.44678497314453</v>
+        <v>64.44677734375</v>
       </c>
     </row>
     <row r="1217">
@@ -12585,7 +12585,7 @@
         </is>
       </c>
       <c r="B1217" t="n">
-        <v>64.85379791259766</v>
+        <v>64.85380554199219</v>
       </c>
     </row>
     <row r="1218">
@@ -12625,7 +12625,7 @@
         </is>
       </c>
       <c r="B1221" t="n">
-        <v>70.18141174316406</v>
+        <v>70.18140411376953</v>
       </c>
     </row>
     <row r="1222">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="B1222" t="n">
-        <v>69.16834259033203</v>
+        <v>69.1683349609375</v>
       </c>
     </row>
     <row r="1223">
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="B1223" t="n">
-        <v>68.59849548339844</v>
+        <v>68.59850311279297</v>
       </c>
     </row>
     <row r="1224">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="B1224" t="n">
-        <v>68.82463073730469</v>
+        <v>68.82462310791016</v>
       </c>
     </row>
     <row r="1225">
@@ -12695,7 +12695,7 @@
         </is>
       </c>
       <c r="B1228" t="n">
-        <v>71.56531524658203</v>
+        <v>71.56532287597656</v>
       </c>
     </row>
     <row r="1229">
@@ -12705,7 +12705,7 @@
         </is>
       </c>
       <c r="B1229" t="n">
-        <v>71.77333831787109</v>
+        <v>71.77335357666016</v>
       </c>
     </row>
     <row r="1230">
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="B1231" t="n">
-        <v>71.56531524658203</v>
+        <v>71.56532287597656</v>
       </c>
     </row>
     <row r="1232">
@@ -12735,7 +12735,7 @@
         </is>
       </c>
       <c r="B1232" t="n">
-        <v>72.08992767333984</v>
+        <v>72.08992004394531</v>
       </c>
     </row>
     <row r="1233">
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="B1235" t="n">
-        <v>72.14420318603516</v>
+        <v>72.14421081542969</v>
       </c>
     </row>
     <row r="1236">
@@ -12795,7 +12795,7 @@
         </is>
       </c>
       <c r="B1238" t="n">
-        <v>73.39244079589844</v>
+        <v>73.39242553710938</v>
       </c>
     </row>
     <row r="1239">
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="B1241" t="n">
-        <v>76.29593658447266</v>
+        <v>76.29592895507812</v>
       </c>
     </row>
     <row r="1242">
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="B1242" t="n">
-        <v>75.78939819335938</v>
+        <v>75.78939056396484</v>
       </c>
     </row>
     <row r="1243">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="B1245" t="n">
-        <v>75.65373229980469</v>
+        <v>75.65372467041016</v>
       </c>
     </row>
     <row r="1246">
@@ -12875,7 +12875,7 @@
         </is>
       </c>
       <c r="B1246" t="n">
-        <v>75.86175537109375</v>
+        <v>75.86176300048828</v>
       </c>
     </row>
     <row r="1247">
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="B1247" t="n">
-        <v>75.8165283203125</v>
+        <v>75.81653594970703</v>
       </c>
     </row>
     <row r="1248">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="B1248" t="n">
-        <v>78.72002410888672</v>
+        <v>78.72003173828125</v>
       </c>
     </row>
     <row r="1249">
@@ -12915,7 +12915,7 @@
         </is>
       </c>
       <c r="B1250" t="n">
-        <v>79.85068511962891</v>
+        <v>79.85069274902344</v>
       </c>
     </row>
     <row r="1251">
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="B1251" t="n">
-        <v>79.66976928710938</v>
+        <v>79.66978454589844</v>
       </c>
     </row>
     <row r="1252">
@@ -12935,7 +12935,7 @@
         </is>
       </c>
       <c r="B1252" t="n">
-        <v>80.27580261230469</v>
+        <v>80.27581024169922</v>
       </c>
     </row>
     <row r="1253">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="B1254" t="n">
-        <v>80.00215911865234</v>
+        <v>80.00216674804688</v>
       </c>
     </row>
     <row r="1255">
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="B1255" t="n">
-        <v>80.3134765625</v>
+        <v>80.31349182128906</v>
       </c>
     </row>
     <row r="1256">
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="B1256" t="n">
-        <v>80.90867614746094</v>
+        <v>80.90868377685547</v>
       </c>
     </row>
     <row r="1257">
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="B1257" t="n">
-        <v>81.30241394042969</v>
+        <v>81.30240631103516</v>
       </c>
     </row>
     <row r="1258">
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="B1258" t="n">
-        <v>81.87928771972656</v>
+        <v>81.87928009033203</v>
       </c>
     </row>
     <row r="1259">
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="B1259" t="n">
-        <v>80.90867614746094</v>
+        <v>80.90868377685547</v>
       </c>
     </row>
     <row r="1260">
@@ -13015,7 +13015,7 @@
         </is>
       </c>
       <c r="B1260" t="n">
-        <v>81.60459136962891</v>
+        <v>81.60458374023438</v>
       </c>
     </row>
     <row r="1261">
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="B1261" t="n">
-        <v>79.65421295166016</v>
+        <v>79.65420532226562</v>
       </c>
     </row>
     <row r="1262">
@@ -13035,7 +13035,7 @@
         </is>
       </c>
       <c r="B1262" t="n">
-        <v>79.50769805908203</v>
+        <v>79.5076904296875</v>
       </c>
     </row>
     <row r="1263">
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="B1263" t="n">
-        <v>79.30625915527344</v>
+        <v>79.30625152587891</v>
       </c>
     </row>
     <row r="1264">
@@ -13065,7 +13065,7 @@
         </is>
       </c>
       <c r="B1265" t="n">
-        <v>79.90144348144531</v>
+        <v>79.90142822265625</v>
       </c>
     </row>
     <row r="1266">
@@ -13075,7 +13075,7 @@
         </is>
       </c>
       <c r="B1266" t="n">
-        <v>79.99300384521484</v>
+        <v>79.99301147460938</v>
       </c>
     </row>
     <row r="1267">
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="B1267" t="n">
-        <v>79.25131988525391</v>
+        <v>79.25133514404297</v>
       </c>
     </row>
     <row r="1268">
@@ -13105,7 +13105,7 @@
         </is>
       </c>
       <c r="B1269" t="n">
-        <v>79.14143371582031</v>
+        <v>79.14144134521484</v>
       </c>
     </row>
     <row r="1270">
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="B1271" t="n">
-        <v>77.27345275878906</v>
+        <v>77.27346038818359</v>
       </c>
     </row>
     <row r="1272">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="B1272" t="n">
-        <v>78.19828796386719</v>
+        <v>78.19830322265625</v>
       </c>
     </row>
     <row r="1273">
@@ -13145,7 +13145,7 @@
         </is>
       </c>
       <c r="B1273" t="n">
-        <v>78.66529083251953</v>
+        <v>78.66529846191406</v>
       </c>
     </row>
     <row r="1274">
@@ -13165,7 +13165,7 @@
         </is>
       </c>
       <c r="B1275" t="n">
-        <v>77.00791931152344</v>
+        <v>77.00792694091797</v>
       </c>
     </row>
     <row r="1276">
@@ -13185,7 +13185,7 @@
         </is>
       </c>
       <c r="B1277" t="n">
-        <v>77.77709197998047</v>
+        <v>77.77707672119141</v>
       </c>
     </row>
     <row r="1278">
@@ -13195,7 +13195,7 @@
         </is>
       </c>
       <c r="B1278" t="n">
-        <v>78.28986358642578</v>
+        <v>78.28984832763672</v>
       </c>
     </row>
     <row r="1279">
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="B1279" t="n">
-        <v>77.55731201171875</v>
+        <v>77.55732727050781</v>
       </c>
     </row>
     <row r="1280">
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="B1280" t="n">
-        <v>76.81562042236328</v>
+        <v>76.81562805175781</v>
       </c>
     </row>
     <row r="1281">
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="B1281" t="n">
-        <v>78.20745849609375</v>
+        <v>78.20745086669922</v>
       </c>
     </row>
     <row r="1282">
@@ -13235,7 +13235,7 @@
         </is>
       </c>
       <c r="B1282" t="n">
-        <v>77.23683929443359</v>
+        <v>77.23682403564453</v>
       </c>
     </row>
     <row r="1283">
@@ -13255,7 +13255,7 @@
         </is>
       </c>
       <c r="B1284" t="n">
-        <v>76.63248443603516</v>
+        <v>76.63249206542969</v>
       </c>
     </row>
     <row r="1285">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="B1285" t="n">
-        <v>76.52261352539062</v>
+        <v>76.52262115478516</v>
       </c>
     </row>
     <row r="1286">
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="B1287" t="n">
-        <v>77.26429748535156</v>
+        <v>77.26430511474609</v>
       </c>
     </row>
     <row r="1288">
@@ -13295,7 +13295,7 @@
         </is>
       </c>
       <c r="B1288" t="n">
-        <v>77.28263092041016</v>
+        <v>77.28261566162109</v>
       </c>
     </row>
     <row r="1289">
@@ -13305,7 +13305,7 @@
         </is>
       </c>
       <c r="B1289" t="n">
-        <v>75.68935394287109</v>
+        <v>75.68934631347656</v>
       </c>
     </row>
     <row r="1290">
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="B1291" t="n">
-        <v>78.06093597412109</v>
+        <v>78.06095123291016</v>
       </c>
     </row>
     <row r="1292">
@@ -13335,7 +13335,7 @@
         </is>
       </c>
       <c r="B1292" t="n">
-        <v>77.25515747070312</v>
+        <v>77.25514984130859</v>
       </c>
     </row>
     <row r="1293">
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="B1293" t="n">
-        <v>77.1177978515625</v>
+        <v>77.11780548095703</v>
       </c>
     </row>
     <row r="1294">
@@ -13355,7 +13355,7 @@
         </is>
       </c>
       <c r="B1294" t="n">
-        <v>77.54817199707031</v>
+        <v>77.54816436767578</v>
       </c>
     </row>
     <row r="1295">
@@ -13385,7 +13385,7 @@
         </is>
       </c>
       <c r="B1297" t="n">
-        <v>76.80648040771484</v>
+        <v>76.80646514892578</v>
       </c>
     </row>
     <row r="1298">
@@ -13395,7 +13395,7 @@
         </is>
       </c>
       <c r="B1298" t="n">
-        <v>76.89804840087891</v>
+        <v>76.89804077148438</v>
       </c>
     </row>
     <row r="1299">
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="B1300" t="n">
-        <v>78.33563995361328</v>
+        <v>78.33564758300781</v>
       </c>
     </row>
     <row r="1301">
@@ -13425,7 +13425,7 @@
         </is>
       </c>
       <c r="B1301" t="n">
-        <v>79.26961517333984</v>
+        <v>79.26962280273438</v>
       </c>
     </row>
     <row r="1302">
@@ -13445,7 +13445,7 @@
         </is>
       </c>
       <c r="B1303" t="n">
-        <v>79.04071044921875</v>
+        <v>79.04071807861328</v>
       </c>
     </row>
     <row r="1304">
@@ -13465,7 +13465,7 @@
         </is>
       </c>
       <c r="B1305" t="n">
-        <v>79.41614532470703</v>
+        <v>79.4161376953125</v>
       </c>
     </row>
     <row r="1306">
@@ -13475,7 +13475,7 @@
         </is>
       </c>
       <c r="B1306" t="n">
-        <v>80.33180236816406</v>
+        <v>80.33180999755859</v>
       </c>
     </row>
     <row r="1307">
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="B1307" t="n">
-        <v>79.94721984863281</v>
+        <v>79.94721221923828</v>
       </c>
     </row>
     <row r="1308">
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="B1308" t="n">
-        <v>79.77326202392578</v>
+        <v>79.77324676513672</v>
       </c>
     </row>
     <row r="1309">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="B1309" t="n">
-        <v>79.370361328125</v>
+        <v>79.37034606933594</v>
       </c>
     </row>
     <row r="1310">
@@ -13515,7 +13515,7 @@
         </is>
       </c>
       <c r="B1310" t="n">
-        <v>78.17996978759766</v>
+        <v>78.17997741699219</v>
       </c>
     </row>
     <row r="1311">
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="B1311" t="n">
-        <v>78.00600433349609</v>
+        <v>78.00598907470703</v>
       </c>
     </row>
     <row r="1312">
@@ -13545,7 +13545,7 @@
         </is>
       </c>
       <c r="B1313" t="n">
-        <v>78.01514434814453</v>
+        <v>78.01515197753906</v>
       </c>
     </row>
     <row r="1314">
@@ -13565,7 +13565,7 @@
         </is>
       </c>
       <c r="B1315" t="n">
-        <v>79.09563446044922</v>
+        <v>79.09564208984375</v>
       </c>
     </row>
     <row r="1316">
@@ -13575,7 +13575,7 @@
         </is>
       </c>
       <c r="B1316" t="n">
-        <v>78.10011291503906</v>
+        <v>78.10012054443359</v>
       </c>
     </row>
     <row r="1317">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="B1317" t="n">
-        <v>77.61989593505859</v>
+        <v>77.61990356445312</v>
       </c>
     </row>
     <row r="1318">
@@ -13595,7 +13595,7 @@
         </is>
       </c>
       <c r="B1318" t="n">
-        <v>77.30590057373047</v>
+        <v>77.305908203125</v>
       </c>
     </row>
     <row r="1319">
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="B1320" t="n">
-        <v>79.86400604248047</v>
+        <v>79.86399078369141</v>
       </c>
     </row>
     <row r="1321">
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="B1321" t="n">
-        <v>78.52491760253906</v>
+        <v>78.52492523193359</v>
       </c>
     </row>
     <row r="1322">
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="B1322" t="n">
-        <v>77.53678131103516</v>
+        <v>77.53678894042969</v>
       </c>
     </row>
     <row r="1323">
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="B1323" t="n">
-        <v>77.61989593505859</v>
+        <v>77.61990356445312</v>
       </c>
     </row>
     <row r="1324">
@@ -13655,7 +13655,7 @@
         </is>
       </c>
       <c r="B1324" t="n">
-        <v>77.1212158203125</v>
+        <v>77.12120819091797</v>
       </c>
     </row>
     <row r="1325">
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="B1328" t="n">
-        <v>76.10536193847656</v>
+        <v>76.10537719726562</v>
       </c>
     </row>
     <row r="1329">
@@ -13725,7 +13725,7 @@
         </is>
       </c>
       <c r="B1331" t="n">
-        <v>74.17526245117188</v>
+        <v>74.17525482177734</v>
       </c>
     </row>
     <row r="1332">
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B1335" t="n">
-        <v>72.95624542236328</v>
+        <v>72.95623779296875</v>
       </c>
     </row>
     <row r="1336">
@@ -13785,7 +13785,7 @@
         </is>
       </c>
       <c r="B1337" t="n">
-        <v>74.27684783935547</v>
+        <v>74.27685546875</v>
       </c>
     </row>
     <row r="1338">
@@ -13805,7 +13805,7 @@
         </is>
       </c>
       <c r="B1339" t="n">
-        <v>73.99056243896484</v>
+        <v>73.99057006835938</v>
       </c>
     </row>
     <row r="1340">
@@ -13815,7 +13815,7 @@
         </is>
       </c>
       <c r="B1340" t="n">
-        <v>74.02750396728516</v>
+        <v>74.02749633789062</v>
       </c>
     </row>
     <row r="1341">
@@ -13845,7 +13845,7 @@
         </is>
       </c>
       <c r="B1343" t="n">
-        <v>73.54727935791016</v>
+        <v>73.54728698730469</v>
       </c>
     </row>
     <row r="1344">
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="B1344" t="n">
-        <v>74.58158874511719</v>
+        <v>74.58159637451172</v>
       </c>
     </row>
     <row r="1345">
@@ -13865,7 +13865,7 @@
         </is>
       </c>
       <c r="B1345" t="n">
-        <v>75.08028411865234</v>
+        <v>75.08029174804688</v>
       </c>
     </row>
     <row r="1346">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="B1346" t="n">
-        <v>75.14493560791016</v>
+        <v>75.14492034912109</v>
       </c>
     </row>
     <row r="1347">
@@ -13905,7 +13905,7 @@
         </is>
       </c>
       <c r="B1349" t="n">
-        <v>76.76105499267578</v>
+        <v>76.76104736328125</v>
       </c>
     </row>
     <row r="1350">
@@ -13925,7 +13925,7 @@
         </is>
       </c>
       <c r="B1351" t="n">
-        <v>76.79798126220703</v>
+        <v>76.79798889160156</v>
       </c>
     </row>
     <row r="1352">
@@ -13935,7 +13935,7 @@
         </is>
       </c>
       <c r="B1352" t="n">
-        <v>77.3890380859375</v>
+        <v>77.38903045654297</v>
       </c>
     </row>
     <row r="1353">
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="B1355" t="n">
-        <v>78.3956298828125</v>
+        <v>78.39563751220703</v>
       </c>
     </row>
     <row r="1356">
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="B1356" t="n">
-        <v>77.93387603759766</v>
+        <v>77.93389129638672</v>
       </c>
     </row>
     <row r="1357">
@@ -13985,7 +13985,7 @@
         </is>
       </c>
       <c r="B1357" t="n">
-        <v>77.90617370605469</v>
+        <v>77.90616607666016</v>
       </c>
     </row>
     <row r="1358">
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="B1358" t="n">
-        <v>77.20433044433594</v>
+        <v>77.20432281494141</v>
       </c>
     </row>
     <row r="1359">
@@ -14015,7 +14015,7 @@
         </is>
       </c>
       <c r="B1360" t="n">
-        <v>75.59744262695312</v>
+        <v>75.59743499755859</v>
       </c>
     </row>
     <row r="1361">
@@ -14025,7 +14025,7 @@
         </is>
       </c>
       <c r="B1361" t="n">
-        <v>75.09876251220703</v>
+        <v>75.0987548828125</v>
       </c>
     </row>
     <row r="1362">
@@ -14035,7 +14035,7 @@
         </is>
       </c>
       <c r="B1362" t="n">
-        <v>74.36919403076172</v>
+        <v>74.36917877197266</v>
       </c>
     </row>
     <row r="1363">
@@ -14075,7 +14075,7 @@
         </is>
       </c>
       <c r="B1366" t="n">
-        <v>77.28742980957031</v>
+        <v>77.28743743896484</v>
       </c>
     </row>
     <row r="1367">
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="B1369" t="n">
-        <v>76.61328887939453</v>
+        <v>76.61329650878906</v>
       </c>
     </row>
     <row r="1370">
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>76.59482574462891</v>
+        <v>76.59481811523438</v>
       </c>
     </row>
     <row r="1372">
@@ -14135,7 +14135,7 @@
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>77.27820587158203</v>
+        <v>77.2781982421875</v>
       </c>
     </row>
     <row r="1373">
@@ -14165,7 +14165,7 @@
         </is>
       </c>
       <c r="B1375" t="n">
-        <v>77.26897430419922</v>
+        <v>77.26895904541016</v>
       </c>
     </row>
     <row r="1376">
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>77.35208129882812</v>
+        <v>77.35208892822266</v>
       </c>
     </row>
     <row r="1378">
@@ -14205,7 +14205,7 @@
         </is>
       </c>
       <c r="B1379" t="n">
-        <v>78.14628601074219</v>
+        <v>78.14630126953125</v>
       </c>
     </row>
     <row r="1380">
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="B1384" t="n">
-        <v>77.57504272460938</v>
+        <v>77.57503509521484</v>
       </c>
     </row>
     <row r="1385">
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>77.93967437744141</v>
+        <v>77.93966674804688</v>
       </c>
     </row>
     <row r="1386">
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="B1386" t="n">
-        <v>77.86488342285156</v>
+        <v>77.86487579345703</v>
       </c>
     </row>
     <row r="1387">
@@ -14325,7 +14325,7 @@
         </is>
       </c>
       <c r="B1391" t="n">
-        <v>81.15601348876953</v>
+        <v>81.15599822998047</v>
       </c>
     </row>
     <row r="1392">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>83.33449554443359</v>
+        <v>83.33448791503906</v>
       </c>
     </row>
     <row r="1395">
@@ -14385,7 +14385,7 @@
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>83.01659393310547</v>
+        <v>83.0166015625</v>
       </c>
     </row>
     <row r="1398">
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>83.87678527832031</v>
+        <v>83.87677764892578</v>
       </c>
     </row>
     <row r="1399">
@@ -14405,7 +14405,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>83.81133270263672</v>
+        <v>83.81132507324219</v>
       </c>
     </row>
     <row r="1400">
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>82.57715606689453</v>
+        <v>82.57717132568359</v>
       </c>
     </row>
     <row r="1401">
@@ -14425,7 +14425,7 @@
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>82.30600738525391</v>
+        <v>82.30601501464844</v>
       </c>
     </row>
     <row r="1402">
@@ -14445,7 +14445,7 @@
         </is>
       </c>
       <c r="B1403" t="n">
-        <v>84.17597961425781</v>
+        <v>84.17596435546875</v>
       </c>
     </row>
     <row r="1404">
@@ -14455,7 +14455,7 @@
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>84.83046722412109</v>
+        <v>84.83045196533203</v>
       </c>
     </row>
     <row r="1405">
@@ -14465,7 +14465,7 @@
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>84.53126525878906</v>
+        <v>84.53127288818359</v>
       </c>
     </row>
     <row r="1406">
@@ -14475,7 +14475,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>85.38208770751953</v>
+        <v>85.38209533691406</v>
       </c>
     </row>
     <row r="1407">
@@ -14505,7 +14505,7 @@
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>84.53126525878906</v>
+        <v>84.53127288818359</v>
       </c>
     </row>
     <row r="1410">
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>83.95156860351562</v>
+        <v>83.95157623291016</v>
       </c>
     </row>
     <row r="1411">
@@ -14555,7 +14555,7 @@
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>85.27925109863281</v>
+        <v>85.27923583984375</v>
       </c>
     </row>
     <row r="1415">
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>85.50364685058594</v>
+        <v>85.50363922119141</v>
       </c>
     </row>
     <row r="1416">
@@ -14575,7 +14575,7 @@
         </is>
       </c>
       <c r="B1416" t="n">
-        <v>85.43818664550781</v>
+        <v>85.43817901611328</v>
       </c>
     </row>
     <row r="1417">
@@ -14595,7 +14595,7 @@
         </is>
       </c>
       <c r="B1418" t="n">
-        <v>86.10203552246094</v>
+        <v>86.10202789306641</v>
       </c>
     </row>
     <row r="1419">
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="B1419" t="n">
-        <v>85.99917602539062</v>
+        <v>85.99918365478516</v>
       </c>
     </row>
     <row r="1420">
@@ -14635,7 +14635,7 @@
         </is>
       </c>
       <c r="B1422" t="n">
-        <v>88.61711120605469</v>
+        <v>88.61712646484375</v>
       </c>
     </row>
     <row r="1423">
@@ -14645,7 +14645,7 @@
         </is>
       </c>
       <c r="B1423" t="n">
-        <v>88.5797119140625</v>
+        <v>88.57971954345703</v>
       </c>
     </row>
     <row r="1424">
@@ -14655,7 +14655,7 @@
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>88.71060180664062</v>
+        <v>88.71061706542969</v>
       </c>
     </row>
     <row r="1425">
@@ -14665,7 +14665,7 @@
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>88.36466217041016</v>
+        <v>88.36466979980469</v>
       </c>
     </row>
     <row r="1426">
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B1426" t="n">
-        <v>88.09353637695312</v>
+        <v>88.09352111816406</v>
       </c>
     </row>
     <row r="1427">
@@ -14685,7 +14685,7 @@
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>88.9443359375</v>
+        <v>88.94435119628906</v>
       </c>
     </row>
     <row r="1428">
@@ -14705,7 +14705,7 @@
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>89.15003967285156</v>
+        <v>89.15004730224609</v>
       </c>
     </row>
     <row r="1430">
@@ -14745,7 +14745,7 @@
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>91.06674194335938</v>
+        <v>91.06674957275391</v>
       </c>
     </row>
     <row r="1434">
@@ -14765,7 +14765,7 @@
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>91.2724609375</v>
+        <v>91.27244567871094</v>
       </c>
     </row>
     <row r="1436">
@@ -14775,7 +14775,7 @@
         </is>
       </c>
       <c r="B1436" t="n">
-        <v>92.22611999511719</v>
+        <v>92.22612762451172</v>
       </c>
     </row>
     <row r="1437">
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="B1437" t="n">
-        <v>92.53467559814453</v>
+        <v>92.53466796875</v>
       </c>
     </row>
     <row r="1438">
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>91.8895263671875</v>
+        <v>91.88953399658203</v>
       </c>
     </row>
     <row r="1439">
@@ -14815,7 +14815,7 @@
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>91.79602813720703</v>
+        <v>91.79603576660156</v>
       </c>
     </row>
     <row r="1441">
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="B1441" t="n">
-        <v>91.43140411376953</v>
+        <v>91.431396484375</v>
       </c>
     </row>
     <row r="1442">
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>91.13597869873047</v>
+        <v>91.135986328125</v>
       </c>
     </row>
     <row r="1447">
@@ -14885,7 +14885,7 @@
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>91.8525390625</v>
+        <v>91.85253143310547</v>
       </c>
     </row>
     <row r="1448">
@@ -14895,7 +14895,7 @@
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>91.258544921875</v>
+        <v>91.25855255126953</v>
       </c>
     </row>
     <row r="1449">
@@ -14915,7 +14915,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>90.10826873779297</v>
+        <v>90.10826110839844</v>
       </c>
     </row>
     <row r="1451">
@@ -14925,7 +14925,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>89.67456817626953</v>
+        <v>89.674560546875</v>
       </c>
     </row>
     <row r="1452">
@@ -14935,7 +14935,7 @@
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>88.88256072998047</v>
+        <v>88.882568359375</v>
       </c>
     </row>
     <row r="1453">
@@ -14945,7 +14945,7 @@
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>89.06169891357422</v>
+        <v>89.06170654296875</v>
       </c>
     </row>
     <row r="1454">
@@ -14955,7 +14955,7 @@
         </is>
       </c>
       <c r="B1454" t="n">
-        <v>89.15597534179688</v>
+        <v>89.15599060058594</v>
       </c>
     </row>
     <row r="1455">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>88.36399841308594</v>
+        <v>88.36399078369141</v>
       </c>
     </row>
     <row r="1456">
@@ -14975,7 +14975,7 @@
         </is>
       </c>
       <c r="B1456" t="n">
-        <v>89.36341857910156</v>
+        <v>89.36342620849609</v>
       </c>
     </row>
     <row r="1457">
@@ -14985,7 +14985,7 @@
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>89.90083312988281</v>
+        <v>89.90084075927734</v>
       </c>
     </row>
     <row r="1458">
@@ -14995,7 +14995,7 @@
         </is>
       </c>
       <c r="B1458" t="n">
-        <v>90.98513031005859</v>
+        <v>90.98512268066406</v>
       </c>
     </row>
     <row r="1459">
@@ -15015,7 +15015,7 @@
         </is>
       </c>
       <c r="B1460" t="n">
-        <v>91.258544921875</v>
+        <v>91.25855255126953</v>
       </c>
     </row>
     <row r="1461">
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>91.93739318847656</v>
+        <v>91.93740081787109</v>
       </c>
     </row>
     <row r="1462">
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="B1462" t="n">
-        <v>90.13655090332031</v>
+        <v>90.13655853271484</v>
       </c>
     </row>
     <row r="1463">
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>90.2685546875</v>
+        <v>90.26856231689453</v>
       </c>
     </row>
     <row r="1464">
@@ -15065,7 +15065,7 @@
         </is>
       </c>
       <c r="B1465" t="n">
-        <v>91.12655639648438</v>
+        <v>91.12654876708984</v>
       </c>
     </row>
     <row r="1466">
@@ -15075,7 +15075,7 @@
         </is>
       </c>
       <c r="B1466" t="n">
-        <v>90.2685546875</v>
+        <v>90.26856231689453</v>
       </c>
     </row>
     <row r="1467">
@@ -15085,7 +15085,7 @@
         </is>
       </c>
       <c r="B1467" t="n">
-        <v>90.55141448974609</v>
+        <v>90.55140686035156</v>
       </c>
     </row>
     <row r="1468">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="B1468" t="n">
-        <v>89.90083312988281</v>
+        <v>89.90084075927734</v>
       </c>
     </row>
     <row r="1469">
@@ -15125,7 +15125,7 @@
         </is>
       </c>
       <c r="B1471" t="n">
-        <v>87.78885650634766</v>
+        <v>87.78886413574219</v>
       </c>
     </row>
     <row r="1472">
@@ -15135,7 +15135,7 @@
         </is>
       </c>
       <c r="B1472" t="n">
-        <v>88.75054931640625</v>
+        <v>88.75056457519531</v>
       </c>
     </row>
     <row r="1473">
@@ -15145,7 +15145,7 @@
         </is>
       </c>
       <c r="B1473" t="n">
-        <v>89.92913055419922</v>
+        <v>89.92911529541016</v>
       </c>
     </row>
     <row r="1474">
@@ -15155,7 +15155,7 @@
         </is>
       </c>
       <c r="B1474" t="n">
-        <v>88.01513671875</v>
+        <v>88.01512908935547</v>
       </c>
     </row>
     <row r="1475">
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="B1475" t="n">
-        <v>89.07113647460938</v>
+        <v>89.07112121582031</v>
       </c>
     </row>
     <row r="1476">
@@ -15175,7 +15175,7 @@
         </is>
       </c>
       <c r="B1476" t="n">
-        <v>90.40054321289062</v>
+        <v>90.40055847167969</v>
       </c>
     </row>
     <row r="1477">
@@ -15195,7 +15195,7 @@
         </is>
       </c>
       <c r="B1478" t="n">
-        <v>88.70341491699219</v>
+        <v>88.70342254638672</v>
       </c>
     </row>
     <row r="1479">
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="B1479" t="n">
-        <v>89.19369506835938</v>
+        <v>89.19371032714844</v>
       </c>
     </row>
     <row r="1480">
@@ -15245,7 +15245,7 @@
         </is>
       </c>
       <c r="B1483" t="n">
-        <v>89.51427459716797</v>
+        <v>89.5142822265625</v>
       </c>
     </row>
     <row r="1484">
@@ -15255,7 +15255,7 @@
         </is>
       </c>
       <c r="B1484" t="n">
-        <v>89.40113830566406</v>
+        <v>89.40113067626953</v>
       </c>
     </row>
     <row r="1485">
@@ -15285,7 +15285,7 @@
         </is>
       </c>
       <c r="B1487" t="n">
-        <v>92.00339508056641</v>
+        <v>92.00340270996094</v>
       </c>
     </row>
     <row r="1488">
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="B1488" t="n">
-        <v>92.37110900878906</v>
+        <v>92.37111663818359</v>
       </c>
     </row>
     <row r="1489">
@@ -15305,7 +15305,7 @@
         </is>
       </c>
       <c r="B1489" t="n">
-        <v>92.96510314941406</v>
+        <v>92.96509552001953</v>
       </c>
     </row>
     <row r="1490">
@@ -15345,7 +15345,7 @@
         </is>
       </c>
       <c r="B1493" t="n">
-        <v>90.49484252929688</v>
+        <v>90.49485015869141</v>
       </c>
     </row>
     <row r="1494">
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="B1494" t="n">
-        <v>90.27797698974609</v>
+        <v>90.27796936035156</v>
       </c>
     </row>
     <row r="1495">
@@ -15365,7 +15365,7 @@
         </is>
       </c>
       <c r="B1495" t="n">
-        <v>90.14598846435547</v>
+        <v>90.14598083496094</v>
       </c>
     </row>
     <row r="1496">
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="B1496" t="n">
-        <v>90.40054321289062</v>
+        <v>90.40055847167969</v>
       </c>
     </row>
     <row r="1497">
@@ -15385,7 +15385,7 @@
         </is>
       </c>
       <c r="B1497" t="n">
-        <v>89.08999633789062</v>
+        <v>89.08998107910156</v>
       </c>
     </row>
     <row r="1498">
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="B1498" t="n">
-        <v>88.88256072998047</v>
+        <v>88.882568359375</v>
       </c>
     </row>
     <row r="1499">
@@ -15415,7 +15415,7 @@
         </is>
       </c>
       <c r="B1500" t="n">
-        <v>88.48655700683594</v>
+        <v>88.486572265625</v>
       </c>
     </row>
     <row r="1501">
@@ -15435,7 +15435,7 @@
         </is>
       </c>
       <c r="B1502" t="n">
-        <v>87.75113677978516</v>
+        <v>87.75115203857422</v>
       </c>
     </row>
     <row r="1503">
@@ -15475,7 +15475,7 @@
         </is>
       </c>
       <c r="B1506" t="n">
-        <v>84.55426025390625</v>
+        <v>84.55426788330078</v>
       </c>
     </row>
     <row r="1507">
@@ -15485,7 +15485,7 @@
         </is>
       </c>
       <c r="B1507" t="n">
-        <v>85.11593627929688</v>
+        <v>85.11592864990234</v>
       </c>
     </row>
     <row r="1508">
@@ -15515,7 +15515,7 @@
         </is>
       </c>
       <c r="B1510" t="n">
-        <v>84.06875610351562</v>
+        <v>84.06874847412109</v>
       </c>
     </row>
   </sheetData>
